--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1450,46 +1450,43 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>101001</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeMeleeArea</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" s="0" t="inlineStr">
-        <is>
-          <t>0.5,1,1</t>
-        </is>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P5" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="U5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="W5" s="0" t="inlineStr">
-        <is>
-          <t>普通近战范围-前方镰刀打击</t>
+      <c r="A5" t="n">
+        <v>100002</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AttackModeMeleeMulti</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>200002</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>hit_times:2&amp;hit_interval:0.1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>近战多段攻击（盗贼：1次攻击2段伤害，间隔0.1秒）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>101002</v>
+        <v>101001</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
@@ -1497,78 +1494,73 @@
         </is>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>1.5</v>
+        <v>24</v>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>0.5,1,1</t>
+        </is>
       </c>
       <c r="K6" s="0" t="n">
-        <v>700001</v>
+        <v>400003</v>
       </c>
       <c r="O6" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>420008</v>
+        <v>200007</v>
       </c>
       <c r="U6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
-          <t>普通近战范围-捶地攻击</t>
+          <t>普通近战范围-前方镰刀打击</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>101003</v>
+        <v>101002</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantArea</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
-        </is>
+          <t>AttackModeMeleeArea</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="I7" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="O7" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>420007</v>
+        <v>420008</v>
       </c>
       <c r="U7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="0" t="inlineStr">
-        <is>
-          <t>dr_damage_rate:2&amp;hp_damage_rate:0.5&amp;hit_decay:1</t>
-        </is>
-      </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
-          <t>远程瞬时-捶地火锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%烧伤）</t>
+          <t>普通近战范围-捶地攻击</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>101004</v>
+        <v>101003</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
@@ -1577,7 +1569,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="I8" s="0" t="n">
@@ -1587,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="O8" s="0" t="n">
         <v>100001</v>
@@ -1605,73 +1597,64 @@
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>远程瞬时-捶地冰锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%冰缓）</t>
+          <t>远程瞬时-捶地火锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="1">
       <c r="A9" s="0" t="n">
-        <v>101005</v>
+        <v>101004</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMeleeArea</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>3</v>
+          <t>AttackModeInstantArea</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
       </c>
       <c r="I9" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
-        <is>
-          <t>0.5,1,0.4</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>400001</t>
-        </is>
-      </c>
-      <c r="M9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>800002</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="S9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="0" t="n">
-        <v>0</v>
+        <v>420007</v>
       </c>
       <c r="U9" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="V9" s="0" t="inlineStr">
+        <is>
+          <t>dr_damage_rate:2&amp;hp_damage_rate:0.5&amp;hit_decay:1</t>
+        </is>
+      </c>
       <c r="W9" s="0" t="inlineStr">
         <is>
-          <t>普通近战范围-前方挥砍(攻击前方1单位,只打本路,最多命中3个敌人)</t>
+          <t>远程瞬时-捶地冰锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%冰缓）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="1">
       <c r="A10" s="0" t="n">
-        <v>101006</v>
+        <v>101005</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
           <t>AttackModeMeleeArea</t>
         </is>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H10" s="0" t="n">
         <v>3</v>
@@ -1681,11 +1664,19 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>0.5,1,1</t>
-        </is>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>400003</v>
+          <t>0.5,1,0.4</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>100001</v>
@@ -1693,18 +1684,24 @@
       <c r="P10" s="0" t="n">
         <v>200007</v>
       </c>
+      <c r="S10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="W10" s="0" t="inlineStr">
         <is>
-          <t>普通近战范围-前方挥砍(大剑战士BOSS普攻,同战之魅魔)</t>
+          <t>普通近战范围-前方挥砍(攻击前方1单位,只打本路,最多命中3个敌人)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="1">
       <c r="A11" s="0" t="n">
-        <v>102001</v>
+        <v>101006</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
@@ -1719,11 +1716,11 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>3,1,0.25</t>
+          <t>0.5,1,1</t>
         </is>
       </c>
       <c r="K11" s="0" t="n">
-        <v>400002</v>
+        <v>400003</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>100001</v>
@@ -1731,92 +1728,88 @@
       <c r="P11" s="0" t="n">
         <v>200007</v>
       </c>
+      <c r="U11" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="W11" s="0" t="inlineStr">
         <is>
+          <t>普通近战范围-前方挥砍(大剑战士BOSS普攻,同战之魅魔)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>102001</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeMeleeArea</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>3,1,0.25</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>400002</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>200007</v>
+      </c>
+      <c r="W12" s="0" t="inlineStr">
+        <is>
           <t>BOSS技能-向前挥砍攻击前方6格</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>102002</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AttackModeMeleeArea</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3,1,1.25</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>400002</v>
-      </c>
-      <c r="O12" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P12" t="n">
-        <v>200007</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>BOSS技能-向前挥砍攻击前方6格上中下3排</t>
         </is>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="1">
       <c r="A13" s="0" t="n">
-        <v>200001</v>
+        <v>102002</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="n"/>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeMeleeArea</t>
         </is>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="0" t="n"/>
-      <c r="M13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>310001</v>
+        <v>3</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>3,1,1.25</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>400002</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P13" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>200007</v>
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击</t>
+          <t>BOSS技能-向前挥砍攻击前方6格上中下3排</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>200002</v>
+        <v>200001</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
@@ -1826,12 +1819,7 @@
       <c r="C14" s="0" t="n"/>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H14" s="0" t="n">
@@ -1841,24 +1829,29 @@
       <c r="M14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="0" t="n">
-        <v>100003</v>
+      <c r="N14" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>420003</v>
+        <v>420011</v>
+      </c>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击</t>
+          <t>远程攻击-攻击</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>200003</v>
+        <v>200002</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1868,12 +1861,12 @@
       <c r="C15" s="0" t="n"/>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H15" s="0" t="n">
@@ -1894,13 +1887,13 @@
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-水球直线攻击</t>
+          <t>远程攻击-火球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>200004</v>
+        <v>200003</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1910,12 +1903,12 @@
       <c r="C16" s="0" t="n"/>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedWaterBall</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="H16" s="0" t="n">
@@ -1925,6 +1918,9 @@
       <c r="M16" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N16" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
@@ -1933,71 +1929,52 @@
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击</t>
+          <t>远程攻击-水球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>201001</v>
+        <v>200004</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedObliqueTracking</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C17" s="0" t="n"/>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I17" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="0" t="n">
-        <v>100001</v>
-      </c>
+      <c r="K17" s="0" t="n"/>
       <c r="M17" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="0" t="n">
-        <v>100003</v>
-      </c>
       <c r="O17" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P17" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="U17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="0" t="inlineStr">
-        <is>
-          <t>aim_up:0.5</t>
-        </is>
+        <v>420003</v>
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
+          <t>远程攻击-冰球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>201002</v>
+        <v>201001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
@@ -2007,12 +1984,12 @@
       <c r="C18" s="0" t="n"/>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H18" s="0" t="n">
@@ -2025,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M18" s="0" t="n">
         <v>1</v>
@@ -2049,37 +2026,44 @@
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>201003</v>
+        <v>201002</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedObliqueTracking</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="n"/>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H19" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I19" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="M19" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N19" s="0" t="n">
         <v>100003</v>
@@ -2090,15 +2074,23 @@
       <c r="P19" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U19" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="0" t="inlineStr">
+        <is>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>201004</v>
+        <v>201003</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
@@ -2107,19 +2099,19 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>1000100001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H20" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M20" s="0" t="n">
         <v>1.5</v>
@@ -2135,37 +2127,37 @@
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>202001</v>
+        <v>201004</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="n"/>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedLove</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
         </is>
       </c>
       <c r="H21" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I21" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="0" t="n"/>
+      <c r="K21" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M21" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N21" s="0" t="n">
         <v>100003</v>
@@ -2174,155 +2166,145 @@
         <v>100001</v>
       </c>
       <c r="P21" s="0" t="n">
-        <v>6</v>
+        <v>420006</v>
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>203001</v>
+        <v>202001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcArea</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr"/>
+          <t>AttackModeRangedTracking</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n"/>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_RangedLove</t>
+        </is>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="n">
-        <v>1900001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="n"/>
       <c r="M22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="0" t="n">
-        <v>100002</v>
+        <v>100003</v>
       </c>
       <c r="O22" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P22" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R22" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="U22" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>204001</v>
+        <v>203001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="n"/>
-      <c r="H23" s="0" t="n"/>
-      <c r="K23" s="0" t="n"/>
-      <c r="M23" s="0" t="n"/>
+          <t>AttackModeRangedArcArea</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr"/>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>1900001</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="N23" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O23" s="0" t="n"/>
-      <c r="P23" s="0" t="n"/>
-      <c r="S23" s="0" t="n">
-        <v>204101</v>
+        <v>100002</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <v>420011</v>
+      </c>
+      <c r="R23" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="U23" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>204002</v>
+        <v>204001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedChain</t>
+          <t>AttackModeRangedSplit</t>
         </is>
       </c>
       <c r="C24" s="0" t="n"/>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="M24" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="H24" s="0" t="n"/>
+      <c r="K24" s="0" t="n"/>
+      <c r="M24" s="0" t="n"/>
       <c r="N24" s="0" t="n">
-        <v>100003</v>
-      </c>
-      <c r="O24" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P24" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="S24" s="0" t="n"/>
-      <c r="U24" s="0" t="n">
-        <v>2</v>
+        <v>310001</v>
+      </c>
+      <c r="O24" s="0" t="n"/>
+      <c r="P24" s="0" t="n"/>
+      <c r="S24" s="0" t="n">
+        <v>204101</v>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>204003</v>
+        <v>204002</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
@@ -2332,12 +2314,12 @@
       <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H25" s="0" t="n">
@@ -2349,7 +2331,7 @@
         </is>
       </c>
       <c r="K25" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M25" s="0" t="n">
         <v>1</v>
@@ -2369,102 +2351,108 @@
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>204101</v>
+        <v>204003</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedChain</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n"/>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N26" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O26" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P26" s="0" t="n">
-        <v>200008</v>
+        <v>420006</v>
+      </c>
+      <c r="S26" s="0" t="n"/>
+      <c r="U26" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>205001</v>
+        <v>204101</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr"/>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K27" s="0" t="n"/>
       <c r="M27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="0" t="n">
-        <v>310001</v>
-      </c>
       <c r="O27" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P27" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R27" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>205002</v>
+        <v>205001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingShrink</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="n"/>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr"/>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
@@ -2475,23 +2463,28 @@
         <v>1</v>
       </c>
       <c r="N28" s="0" t="n">
-        <v>100003</v>
+        <v>310001</v>
       </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>420006</v>
+        <v>200008</v>
+      </c>
+      <c r="R28" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>205003</v>
+        <v>205002</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
@@ -2501,12 +2494,12 @@
       <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
@@ -2527,121 +2520,109 @@
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>205004</v>
+        <v>205003</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMelee</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeRangedPiercingShrink</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n"/>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
       </c>
       <c r="H30" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="K30" s="0" t="n"/>
       <c r="M30" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="0" t="n">
-        <v>0</v>
+        <v>100003</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="S30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="0" t="n">
-        <v>0</v>
+        <v>420006</v>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>普通近战攻击-单体(兽人战士)</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>206001</v>
+        <v>205004</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeMelee</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H31" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="0" t="n">
-        <v>310001</v>
+        <v>0</v>
       </c>
       <c r="O31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R31" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V31" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>200007</v>
+      </c>
+      <c r="S31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>普通近战攻击-单体(兽人战士)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>210001</v>
+        <v>206001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
@@ -2650,72 +2631,87 @@
       <c r="H32" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K32" s="0" t="n"/>
+      <c r="I32" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N32" s="0" t="n">
         <v>310001</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>420011</v>
+        <v>200008</v>
       </c>
       <c r="R32" s="0" t="inlineStr">
         <is>
-          <t>type:2&amp;color:1,1,1</t>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V32" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
         </is>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n"/>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H33" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I33" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K33" s="0" t="n">
-        <v>300002</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K33" s="0" t="n"/>
       <c r="M33" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O33" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T33" s="0" t="n">
-        <v>50</v>
+        <v>420011</v>
+      </c>
+      <c r="R33" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300002</v>
+        <v>300001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -2744,99 +2740,83 @@
         <v>420008</v>
       </c>
       <c r="T34" s="0" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰(敢死队)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300061</v>
+        <v>300002</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H35" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M35" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N35" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O35" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P35" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R35" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S35" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I36" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M36" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>400003</v>
@@ -2863,13 +2843,13 @@
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2891,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2918,13 +2898,13 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
@@ -2946,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>400003</v>
@@ -2973,13 +2953,13 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
@@ -3001,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>400003</v>
@@ -3028,13 +3008,13 @@
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
@@ -3056,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>400003</v>
@@ -3083,47 +3063,49 @@
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="K41" s="0" t="n">
-        <v>1700001</v>
-      </c>
       <c r="M41" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N41" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O41" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P41" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="0" t="n">
-        <v>0</v>
+      <c r="R41" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S41" s="0" t="n">
         <v>0</v>
@@ -3136,133 +3118,143 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr"/>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr"/>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I42" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.5,0.5</t>
         </is>
       </c>
       <c r="K42" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L42" s="0" t="inlineStr"/>
-      <c r="M42" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>1700001</v>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N42" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O42" s="0" t="inlineStr"/>
-      <c r="P42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q42" s="0" t="inlineStr"/>
-      <c r="R42" s="0" t="inlineStr"/>
-      <c r="S42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U42" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="O42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
-      </c>
-      <c r="H43" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I43" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J43" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K43" s="0" t="n"/>
-      <c r="L43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="0" t="n"/>
-      <c r="O43" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P43" s="0" t="n">
-        <v>630005</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr"/>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L43" s="0" t="inlineStr"/>
+      <c r="M43" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N43" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O43" s="0" t="inlineStr"/>
+      <c r="P43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q43" s="0" t="inlineStr"/>
+      <c r="R43" s="0" t="inlineStr"/>
+      <c r="S43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U43" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
@@ -3271,7 +3263,7 @@
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>1000400001:1</t>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H44" s="0" t="n">
@@ -3299,50 +3291,60 @@
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H45" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I45" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K45" s="0" t="n"/>
+      <c r="L45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0" t="n"/>
       <c r="O45" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H46" s="0" t="n">
@@ -3355,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="0" t="n">
-        <v>500003</v>
+        <v>500001</v>
       </c>
       <c r="O46" s="0" t="n">
         <v>100001</v>
@@ -3365,24 +3367,30 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>600001</v>
+        <v>500002</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>500002</v>
+        <v>500003</v>
       </c>
       <c r="O47" s="0" t="n">
         <v>100001</v>
@@ -3392,67 +3400,40 @@
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="n"/>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I48" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J48" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K48" s="0" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="M48" s="0" t="n">
-        <v>1.5</v>
+        <v>500002</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P48" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q48" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V48" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -3462,12 +3443,12 @@
       <c r="C49" s="0" t="n"/>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I49" s="0" t="n">
@@ -3477,7 +3458,7 @@
         <v>1.5</v>
       </c>
       <c r="K49" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="M49" s="0" t="n">
         <v>1.5</v>
@@ -3500,27 +3481,28 @@
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="n"/>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I50" s="0" t="n">
@@ -3530,13 +3512,10 @@
         <v>1.5</v>
       </c>
       <c r="K50" s="0" t="n">
-        <v>800001</v>
+        <v>2000002</v>
       </c>
       <c r="M50" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O50" s="0" t="n">
         <v>100001</v>
@@ -3544,19 +3523,39 @@
       <c r="P50" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q50" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V50" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>800001</v>
+        <v>700003</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I51" s="0" t="n">
@@ -3565,10 +3564,14 @@
       <c r="J51" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K51" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K51" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O51" s="0" t="n">
         <v>100001</v>
@@ -3578,47 +3581,45 @@
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I52" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K52" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P52" s="0" t="n"/>
-      <c r="U52" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O52" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P52" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -3629,7 +3630,7 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>900003</v>
@@ -3642,17 +3643,17 @@
       </c>
       <c r="P53" s="0" t="n"/>
       <c r="U53" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
@@ -3663,7 +3664,7 @@
         <v>11</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>900003</v>
@@ -3676,17 +3677,17 @@
       </c>
       <c r="P54" s="0" t="n"/>
       <c r="U54" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
@@ -3697,7 +3698,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K55" s="0" t="n">
         <v>900003</v>
@@ -3710,17 +3711,17 @@
       </c>
       <c r="P55" s="0" t="n"/>
       <c r="U55" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -3731,7 +3732,7 @@
         <v>11</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>900003</v>
@@ -3744,92 +3745,75 @@
       </c>
       <c r="P56" s="0" t="n"/>
       <c r="U56" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E57" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H57" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M57" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N57" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O57" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P57" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R57" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P57" s="0" t="n"/>
+      <c r="U57" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F58" s="0" t="inlineStr"/>
-      <c r="G58" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H58" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="0" t="inlineStr"/>
-      <c r="K58" s="0" t="inlineStr"/>
-      <c r="L58" s="0" t="inlineStr"/>
       <c r="M58" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N58" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O58" s="0" t="n">
         <v>100001</v>
@@ -3837,43 +3821,35 @@
       <c r="P58" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q58" s="0" t="inlineStr"/>
       <c r="R58" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr"/>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr"/>
       <c r="G59" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H59" s="0" t="n">
         <v>0.3</v>
@@ -3881,15 +3857,22 @@
       <c r="I59" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J59" s="0" t="inlineStr"/>
+      <c r="K59" s="0" t="inlineStr"/>
+      <c r="L59" s="0" t="inlineStr"/>
       <c r="M59" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N59" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P59" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q59" s="0" t="inlineStr"/>
       <c r="R59" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -3906,45 +3889,97 @@
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R60" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D60" s="0" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H61" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M60" s="0" t="n">
+      <c r="M61" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N60" s="0" t="n">
+      <c r="N61" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O60" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P60" s="0" t="n">
+      <c r="O61" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P61" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R60" s="0" t="inlineStr">
+      <c r="R61" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W60" s="0" t="inlineStr">
+      <c r="W61" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1450,35 +1450,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>100002</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>AttackModeMeleeMulti</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="O5" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P5" s="0" t="n">
         <v>200002</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V5" s="0" t="inlineStr">
         <is>
           <t>hit_times:2&amp;hit_interval:0.1</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W5" s="0" t="inlineStr">
         <is>
           <t>近战多段攻击（盗贼：1次攻击2段伤害，间隔0.1秒）</t>
         </is>
@@ -3587,11 +3587,21 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>800001</v>
+        <v>700005</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I52" s="0" t="n">
@@ -3600,10 +3610,11 @@
       <c r="J52" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K52" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K52" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O52" s="0" t="n">
         <v>100001</v>
@@ -3611,83 +3622,95 @@
       <c r="P52" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q52" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300031</v>
+        <v>700006</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
       <c r="I53" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>900003</v>
       </c>
       <c r="M53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P53" s="0" t="n"/>
-      <c r="U53" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P53" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷范围攻击-随机落点(雷大魔法师BOSS技能,瞬发无弹道)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300032</v>
+        <v>800001</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I54" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K54" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P54" s="0" t="n"/>
-      <c r="U54" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300033</v>
+        <v>300031</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
@@ -3698,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K55" s="0" t="n">
         <v>900003</v>
@@ -3711,17 +3734,17 @@
       </c>
       <c r="P55" s="0" t="n"/>
       <c r="U55" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300034</v>
+        <v>300032</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -3732,7 +3755,7 @@
         <v>11</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>900003</v>
@@ -3745,17 +3768,17 @@
       </c>
       <c r="P56" s="0" t="n"/>
       <c r="U56" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300035</v>
+        <v>300033</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
@@ -3766,7 +3789,7 @@
         <v>11</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>900003</v>
@@ -3779,207 +3802,275 @@
       </c>
       <c r="P57" s="0" t="n"/>
       <c r="U57" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300041</v>
+        <v>300034</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D58" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E58" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H58" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M58" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N58" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O58" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P58" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R58" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P58" s="0" t="n"/>
+      <c r="U58" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300051</v>
+        <v>300035</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr"/>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F59" s="0" t="inlineStr"/>
-      <c r="G59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
       </c>
       <c r="I59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="0" t="inlineStr"/>
-      <c r="K59" s="0" t="inlineStr"/>
-      <c r="L59" s="0" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>900003</v>
+      </c>
       <c r="M59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P59" s="0" t="n"/>
+      <c r="U59" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N59" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O59" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P59" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="Q59" s="0" t="inlineStr"/>
-      <c r="R59" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300071</v>
+        <v>300041</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
+          <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G60" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H60" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I60" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N60" s="0" t="n">
-        <v>0</v>
+        <v>310001</v>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P60" s="0" t="n">
         <v>420001</v>
       </c>
       <c r="R60" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr"/>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr"/>
+      <c r="G61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="0" t="inlineStr"/>
+      <c r="K61" s="0" t="inlineStr"/>
+      <c r="L61" s="0" t="inlineStr"/>
+      <c r="M61" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q61" s="0" t="inlineStr"/>
+      <c r="R61" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R62" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B61" s="0" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D61" s="0" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H63" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M61" s="0" t="n">
+      <c r="M63" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="0" t="n">
+      <c r="N63" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O61" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P61" s="0" t="n">
+      <c r="O63" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P63" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R61" s="0" t="inlineStr">
+      <c r="R63" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W61" s="0" t="inlineStr">
+      <c r="W63" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>其它扩展参数(&amp;分隔项,:分键值,按key解析)。stuck_time:射空后弹体插地停留秒数(&gt;0启用,空/0=不插地落地即销毁); stuck_sink:插地下沉深度(默认0,正值向下沉)。插地目前仅AttackModeRangedArcTracking系(抛物线落点跟踪)使用; aim_up:瞄准点相对目标脚底上抬高度(默认0=瞄脚底),目前仅AttackModeRangedObliqueTracking(直线斜射跟踪)使用</t>
+          <t>其它扩展参数(&amp;分隔项,:分键值,按key解析)。stuck_time:射空后弹体插地停留秒数(&gt;0启用,空/0=不插地落地即销毁); stuck_sink:插地下沉深度(默认0,正值向下沉)。插地目前仅AttackModeRangedArcTracking系(抛物线落点跟踪)使用; aim_up:瞄准点相对目标脚底上抬高度(默认0=瞄脚底),目前仅AttackModeRangedObliqueTracking(直线斜射跟踪)使用; shield_count:援护护盾单次套盾的最前排友军数量(默认3); shield_buff:护盾BUFF的ID(默认0=未配置)。援护护盾目前仅AttackModeShieldCast使用</t>
         </is>
       </c>
       <c r="W3" s="0" t="inlineStr">
@@ -1959,6 +1959,9 @@
       <c r="K17" s="0" t="n"/>
       <c r="M17" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O17" s="0" t="n">
         <v>100001</v>
@@ -3405,89 +3408,63 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="n">
-        <v>600001</v>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeLure</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="0" t="n">
-        <v>500002</v>
-      </c>
-      <c r="O48" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P48" s="0" t="n">
+      <c r="A48" t="n">
+        <v>500003</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AttackModeShieldCast</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>500003</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
         <v>470001</v>
       </c>
-      <c r="W48" s="0" t="inlineStr">
-        <is>
-          <t>引诱敌人到当前线路</t>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>shield_count:3&amp;shield_buff:2000700001</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="n"/>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F49" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I49" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J49" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K49" s="0" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="M49" s="0" t="n">
-        <v>1.5</v>
+        <v>500002</v>
       </c>
       <c r="O49" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P49" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q49" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V49" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3497,12 +3474,12 @@
       <c r="C50" s="0" t="n"/>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I50" s="0" t="n">
@@ -3512,7 +3489,7 @@
         <v>1.5</v>
       </c>
       <c r="K50" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>1.5</v>
@@ -3535,27 +3512,28 @@
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="n"/>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I51" s="0" t="n">
@@ -3565,13 +3543,10 @@
         <v>1.5</v>
       </c>
       <c r="K51" s="0" t="n">
-        <v>800001</v>
+        <v>2000002</v>
       </c>
       <c r="M51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O51" s="0" t="n">
         <v>100001</v>
@@ -3579,24 +3554,34 @@
       <c r="P51" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q51" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V51" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>700005</v>
+        <v>700003</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
@@ -3611,10 +3596,13 @@
         <v>1.5</v>
       </c>
       <c r="K52" s="0" t="n">
-        <v>200001</v>
+        <v>800001</v>
       </c>
       <c r="M52" s="0" t="n">
-        <v>1.5</v>
+        <v>3</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O52" s="0" t="n">
         <v>100001</v>
@@ -3622,29 +3610,29 @@
       <c r="P52" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="Q52" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V52" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
-      </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>700006</v>
+        <v>700005</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
           <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall_2</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I53" s="0" t="n">
@@ -3654,7 +3642,7 @@
         <v>1.5</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>900003</v>
+        <v>200001</v>
       </c>
       <c r="M53" s="0" t="n">
         <v>1.5</v>
@@ -3670,19 +3658,24 @@
           <t>0,6,0</t>
         </is>
       </c>
+      <c r="V53" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>落雷范围攻击-随机落点(雷大魔法师BOSS技能,瞬发无弹道)</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>800001</v>
+        <v>700006</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
       <c r="I54" s="0" t="n">
@@ -3691,10 +3684,11 @@
       <c r="J54" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K54" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K54" s="0" t="n">
+        <v>900003</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O54" s="0" t="n">
         <v>100001</v>
@@ -3702,49 +3696,52 @@
       <c r="P54" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q54" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>落雷范围攻击-随机落点(雷大魔法师BOSS技能,瞬发无弹道)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I55" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K55" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P55" s="0" t="n"/>
-      <c r="U55" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K55" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O55" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P55" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -3755,7 +3752,7 @@
         <v>11</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>900003</v>
@@ -3768,17 +3765,17 @@
       </c>
       <c r="P56" s="0" t="n"/>
       <c r="U56" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
@@ -3789,7 +3786,7 @@
         <v>11</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>900003</v>
@@ -3802,17 +3799,17 @@
       </c>
       <c r="P57" s="0" t="n"/>
       <c r="U57" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
@@ -3823,7 +3820,7 @@
         <v>11</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K58" s="0" t="n">
         <v>900003</v>
@@ -3836,17 +3833,17 @@
       </c>
       <c r="P58" s="0" t="n"/>
       <c r="U58" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
@@ -3857,7 +3854,7 @@
         <v>11</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>900003</v>
@@ -3870,92 +3867,75 @@
       </c>
       <c r="P59" s="0" t="n"/>
       <c r="U59" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H60" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M60" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N60" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O60" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P60" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R60" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P60" s="0" t="n"/>
+      <c r="U60" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F61" s="0" t="inlineStr"/>
-      <c r="G61" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H61" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="0" t="inlineStr"/>
-      <c r="K61" s="0" t="inlineStr"/>
-      <c r="L61" s="0" t="inlineStr"/>
       <c r="M61" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N61" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O61" s="0" t="n">
         <v>100001</v>
@@ -3963,43 +3943,35 @@
       <c r="P61" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q61" s="0" t="inlineStr"/>
       <c r="R61" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr"/>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr"/>
       <c r="G62" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H62" s="0" t="n">
         <v>0.3</v>
@@ -4007,15 +3979,22 @@
       <c r="I62" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J62" s="0" t="inlineStr"/>
+      <c r="K62" s="0" t="inlineStr"/>
+      <c r="L62" s="0" t="inlineStr"/>
       <c r="M62" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N62" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O62" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P62" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q62" s="0" t="inlineStr"/>
       <c r="R62" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -4032,45 +4011,97 @@
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R63" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B63" s="0" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D63" s="0" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H64" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M63" s="0" t="n">
+      <c r="M64" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N63" s="0" t="n">
+      <c r="N64" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O63" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P63" s="0" t="n">
+      <c r="O64" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P64" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R63" s="0" t="inlineStr">
+      <c r="R64" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W63" s="0" t="inlineStr">
+      <c r="W64" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -3408,28 +3408,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>500003</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>AttackModeShieldCast</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>500003</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V48" s="0" t="inlineStr">
         <is>
           <t>shield_count:3&amp;shield_buff:2000700001</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W48" s="0" t="inlineStr">
         <is>
           <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
@@ -3675,35 +3675,27 @@
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J54" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K54" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M54" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O54" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P54" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q54" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
+          <t>AttackModeFalluponChainMulti</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="n"/>
+      <c r="J54" s="0" t="n"/>
+      <c r="K54" s="0" t="n"/>
+      <c r="M54" s="0" t="n"/>
+      <c r="O54" s="0" t="n"/>
+      <c r="P54" s="0" t="n"/>
+      <c r="Q54" s="0" t="n"/>
+      <c r="S54" t="n">
+        <v>800001</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>hit_times:3&amp;hit_interval:0.25</t>
         </is>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>落雷范围攻击-随机落点(雷大魔法师BOSS技能,瞬发无弹道)</t>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800001完整普攻雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -3685,17 +3685,17 @@
       <c r="O54" s="0" t="n"/>
       <c r="P54" s="0" t="n"/>
       <c r="Q54" s="0" t="n"/>
-      <c r="S54" t="n">
-        <v>800001</v>
-      </c>
-      <c r="V54" t="inlineStr">
+      <c r="S54" s="0" t="n">
+        <v>800002</v>
+      </c>
+      <c r="V54" s="0" t="inlineStr">
         <is>
           <t>hit_times:3&amp;hit_interval:0.25</t>
         </is>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>天降连锁-三连发发射器(0.5秒内发3次800001完整普攻雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
@@ -3732,42 +3732,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0" t="n">
-        <v>300031</v>
-      </c>
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
-      </c>
-      <c r="I56" s="0" t="n">
+      <c r="A56" t="n">
+        <v>800002</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AttackModeFalluponChain</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
         <v>11</v>
       </c>
-      <c r="J56" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K56" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P56" s="0" t="n"/>
-      <c r="U56" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" s="0" t="inlineStr">
-        <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+      <c r="J56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>900004&amp;900004</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P56" t="n">
+        <v>420008</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
@@ -3778,7 +3776,7 @@
         <v>11</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>900003</v>
@@ -3791,17 +3789,17 @@
       </c>
       <c r="P57" s="0" t="n"/>
       <c r="U57" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
@@ -3812,7 +3810,7 @@
         <v>11</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K58" s="0" t="n">
         <v>900003</v>
@@ -3825,17 +3823,17 @@
       </c>
       <c r="P58" s="0" t="n"/>
       <c r="U58" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
@@ -3846,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>900003</v>
@@ -3859,17 +3857,17 @@
       </c>
       <c r="P59" s="0" t="n"/>
       <c r="U59" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
@@ -3880,7 +3878,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>900003</v>
@@ -3893,92 +3891,75 @@
       </c>
       <c r="P60" s="0" t="n"/>
       <c r="U60" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H61" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M61" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N61" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O61" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P61" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R61" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P61" s="0" t="n"/>
+      <c r="U61" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F62" s="0" t="inlineStr"/>
-      <c r="G62" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H62" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="0" t="inlineStr"/>
-      <c r="K62" s="0" t="inlineStr"/>
-      <c r="L62" s="0" t="inlineStr"/>
       <c r="M62" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N62" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O62" s="0" t="n">
         <v>100001</v>
@@ -3986,43 +3967,35 @@
       <c r="P62" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q62" s="0" t="inlineStr"/>
       <c r="R62" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr"/>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr"/>
       <c r="G63" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H63" s="0" t="n">
         <v>0.3</v>
@@ -4030,15 +4003,22 @@
       <c r="I63" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J63" s="0" t="inlineStr"/>
+      <c r="K63" s="0" t="inlineStr"/>
+      <c r="L63" s="0" t="inlineStr"/>
       <c r="M63" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N63" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P63" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q63" s="0" t="inlineStr"/>
       <c r="R63" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -4055,45 +4035,97 @@
       </c>
       <c r="W63" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R64" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B64" s="0" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D64" s="0" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H65" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M64" s="0" t="n">
+      <c r="M65" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N64" s="0" t="n">
+      <c r="N65" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O64" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P64" s="0" t="n">
+      <c r="O65" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P65" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R64" s="0" t="inlineStr">
+      <c r="R65" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W64" s="0" t="inlineStr">
+      <c r="W65" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -3437,156 +3437,159 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>600001</v>
+        <v>500004</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
-      </c>
-      <c r="J49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="0" t="n">
-        <v>500002</v>
+          <t>AttackModeSummon</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>500002</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="O49" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P49" s="0" t="n">
-        <v>470001</v>
+        <v>0</v>
+      </c>
+      <c r="S49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0</t>
+        </is>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>召唤-骷髅召唤师普攻（自己当前位置召唤1只骷髅战士，5秒一次）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>700001</v>
+        <v>500005</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C50" s="0" t="n"/>
-      <c r="D50" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F50" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
+          <t>AttackModeSummon</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="I50" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K50" s="0" t="n">
-        <v>2000001</v>
+        <v>0</v>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>500002</t>
+        </is>
       </c>
       <c r="M50" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="N50" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="O50" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P50" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q50" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="S50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>gravity:2.4525</t>
+          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1</t>
         </is>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>召唤-骷髅召唤师BOSS技能（自己路+上下相邻路每路3只，独立随机骷髅战士/投手，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>700002</v>
+        <v>600001</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="n"/>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
-        </is>
-      </c>
-      <c r="F51" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
-        </is>
-      </c>
-      <c r="I51" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J51" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="0" t="n">
-        <v>2000002</v>
-      </c>
-      <c r="M51" s="0" t="n">
-        <v>1.5</v>
+        <v>500002</v>
       </c>
       <c r="O51" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P51" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q51" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V51" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>700003</v>
+        <v>700001</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="n"/>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I52" s="0" t="n">
@@ -3596,13 +3599,10 @@
         <v>1.5</v>
       </c>
       <c r="K52" s="0" t="n">
-        <v>800001</v>
+        <v>2000001</v>
       </c>
       <c r="M52" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O52" s="0" t="n">
         <v>100001</v>
@@ -3610,29 +3610,40 @@
       <c r="P52" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q52" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>700005</v>
+        <v>700002</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
           <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
+      <c r="C53" s="0" t="n"/>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall_2</t>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I53" s="0" t="n">
@@ -3642,7 +3653,7 @@
         <v>1.5</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>200001</v>
+        <v>2000002</v>
       </c>
       <c r="M53" s="0" t="n">
         <v>1.5</v>
@@ -3665,47 +3676,73 @@
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>700006</v>
+        <v>700003</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChainMulti</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="n"/>
-      <c r="J54" s="0" t="n"/>
-      <c r="K54" s="0" t="n"/>
-      <c r="M54" s="0" t="n"/>
-      <c r="O54" s="0" t="n"/>
-      <c r="P54" s="0" t="n"/>
-      <c r="Q54" s="0" t="n"/>
-      <c r="S54" s="0" t="n">
-        <v>800002</v>
-      </c>
-      <c r="V54" s="0" t="inlineStr">
-        <is>
-          <t>hit_times:3&amp;hit_interval:0.25</t>
-        </is>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" s="0" t="n">
+        <v>100003</v>
+      </c>
+      <c r="O54" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>800001</v>
+        <v>700005</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall_2</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I55" s="0" t="n">
@@ -3714,10 +3751,11 @@
       <c r="J55" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K55" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K55" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
@@ -3725,115 +3763,119 @@
       <c r="P55" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q55" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V55" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="0" t="n">
+        <v>700006</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeFalluponChainMulti</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="n"/>
+      <c r="J56" s="0" t="n"/>
+      <c r="K56" s="0" t="n"/>
+      <c r="M56" s="0" t="n"/>
+      <c r="O56" s="0" t="n"/>
+      <c r="P56" s="0" t="n"/>
+      <c r="Q56" s="0" t="n"/>
+      <c r="S56" s="0" t="n">
         <v>800002</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>AttackModeFalluponChain</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>11</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>900004&amp;900004</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P56" t="n">
-        <v>420008</v>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
+      <c r="V56" s="0" t="inlineStr">
+        <is>
+          <t>hit_times:3&amp;hit_interval:0.25</t>
+        </is>
+      </c>
+      <c r="W56" s="0" t="inlineStr">
+        <is>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300031</v>
+        <v>800001</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I57" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K57" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P57" s="0" t="n"/>
-      <c r="U57" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O57" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300032</v>
+        <v>800002</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I58" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K58" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P58" s="0" t="n"/>
-      <c r="U58" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t>900004&amp;900004</t>
+        </is>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300033</v>
+        <v>300031</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
@@ -3844,7 +3886,7 @@
         <v>11</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>900003</v>
@@ -3857,17 +3899,17 @@
       </c>
       <c r="P59" s="0" t="n"/>
       <c r="U59" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300034</v>
+        <v>300032</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
@@ -3878,7 +3920,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>900003</v>
@@ -3891,17 +3933,17 @@
       </c>
       <c r="P60" s="0" t="n"/>
       <c r="U60" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300035</v>
+        <v>300033</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -3912,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K61" s="0" t="n">
         <v>900003</v>
@@ -3925,207 +3967,275 @@
       </c>
       <c r="P61" s="0" t="n"/>
       <c r="U61" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300041</v>
+        <v>300034</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H62" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M62" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N62" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O62" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P62" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R62" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P62" s="0" t="n"/>
+      <c r="U62" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300051</v>
+        <v>300035</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C63" s="0" t="inlineStr"/>
-      <c r="D63" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F63" s="0" t="inlineStr"/>
-      <c r="G63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
       </c>
       <c r="I63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="0" t="inlineStr"/>
-      <c r="K63" s="0" t="inlineStr"/>
-      <c r="L63" s="0" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>900003</v>
+      </c>
       <c r="M63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P63" s="0" t="n"/>
+      <c r="U63" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N63" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O63" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P63" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="Q63" s="0" t="inlineStr"/>
-      <c r="R63" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W63" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300071</v>
+        <v>300041</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
+          <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G64" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H64" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I64" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M64" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N64" s="0" t="n">
-        <v>0</v>
+        <v>310001</v>
+      </c>
+      <c r="O64" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P64" s="0" t="n">
         <v>420001</v>
       </c>
       <c r="R64" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W64" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr"/>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr"/>
+      <c r="G65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="0" t="inlineStr"/>
+      <c r="K65" s="0" t="inlineStr"/>
+      <c r="L65" s="0" t="inlineStr"/>
+      <c r="M65" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P65" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q65" s="0" t="inlineStr"/>
+      <c r="R65" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R66" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B65" s="0" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D65" s="0" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H67" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M65" s="0" t="n">
+      <c r="M67" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N65" s="0" t="n">
+      <c r="N67" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O65" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P65" s="0" t="n">
+      <c r="O67" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P67" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R65" s="0" t="inlineStr">
+      <c r="R67" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W65" s="0" t="inlineStr">
+      <c r="W67" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1809,49 +1809,55 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>200001</v>
+        <v>102003</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="n"/>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeInstant</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K14" s="0" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>2100001</v>
+      </c>
       <c r="M14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>310001</v>
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R14" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>420008</v>
+      </c>
+      <c r="S14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击</t>
+          <t>单体瞬时攻击(牧师普攻:瞬间命中无扩散,命中特效Effect_Hit_2)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>200002</v>
+        <v>200001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1861,12 +1867,7 @@
       <c r="C15" s="0" t="n"/>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H15" s="0" t="n">
@@ -1876,24 +1877,29 @@
       <c r="M15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="0" t="n">
-        <v>100003</v>
+      <c r="N15" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>420003</v>
+        <v>420011</v>
+      </c>
+      <c r="R15" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击</t>
+          <t>远程攻击-攻击</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>200003</v>
+        <v>200002</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1903,12 +1909,12 @@
       <c r="C16" s="0" t="n"/>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H16" s="0" t="n">
@@ -1929,13 +1935,13 @@
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-水球直线攻击</t>
+          <t>远程攻击-火球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>200004</v>
+        <v>200003</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1945,12 +1951,12 @@
       <c r="C17" s="0" t="n"/>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedWaterBall</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
@@ -1971,42 +1977,34 @@
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击</t>
+          <t>远程攻击-水球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>201001</v>
+        <v>200004</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedObliqueTracking</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C18" s="0" t="n"/>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="H18" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="0" t="n">
-        <v>100001</v>
-      </c>
+      <c r="K18" s="0" t="n"/>
       <c r="M18" s="0" t="n">
         <v>1</v>
       </c>
@@ -2017,25 +2015,17 @@
         <v>100001</v>
       </c>
       <c r="P18" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="U18" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="0" t="inlineStr">
-        <is>
-          <t>aim_up:0.5</t>
-        </is>
+        <v>420003</v>
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
+          <t>远程攻击-冰球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>201002</v>
+        <v>201001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
@@ -2045,12 +2035,12 @@
       <c r="C19" s="0" t="n"/>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H19" s="0" t="n">
@@ -2063,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M19" s="0" t="n">
         <v>1</v>
@@ -2087,37 +2077,44 @@
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>201003</v>
+        <v>201002</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedObliqueTracking</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="n"/>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H20" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I20" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="M20" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N20" s="0" t="n">
         <v>100003</v>
@@ -2128,15 +2125,23 @@
       <c r="P20" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="0" t="inlineStr">
+        <is>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>201004</v>
+        <v>201003</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
@@ -2145,19 +2150,19 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>1000100001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H21" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M21" s="0" t="n">
         <v>1.5</v>
@@ -2173,37 +2178,37 @@
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>202001</v>
+        <v>201004</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="n"/>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedLove</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
         </is>
       </c>
       <c r="H22" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I22" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="0" t="n"/>
+      <c r="K22" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M22" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N22" s="0" t="n">
         <v>100003</v>
@@ -2212,155 +2217,145 @@
         <v>100001</v>
       </c>
       <c r="P22" s="0" t="n">
-        <v>6</v>
+        <v>420006</v>
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>203001</v>
+        <v>202001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcArea</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr"/>
+          <t>AttackModeRangedTracking</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n"/>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_RangedLove</t>
+        </is>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="n">
-        <v>1900001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="n"/>
       <c r="M23" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="0" t="n">
-        <v>100002</v>
+        <v>100003</v>
       </c>
       <c r="O23" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P23" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R23" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="U23" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>204001</v>
+        <v>203001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="n"/>
-      <c r="H24" s="0" t="n"/>
-      <c r="K24" s="0" t="n"/>
-      <c r="M24" s="0" t="n"/>
+          <t>AttackModeRangedArcArea</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr"/>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>1900001</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O24" s="0" t="n"/>
-      <c r="P24" s="0" t="n"/>
-      <c r="S24" s="0" t="n">
-        <v>204101</v>
+        <v>100002</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>420011</v>
+      </c>
+      <c r="R24" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="U24" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>204002</v>
+        <v>204001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedChain</t>
+          <t>AttackModeRangedSplit</t>
         </is>
       </c>
       <c r="C25" s="0" t="n"/>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
-        </is>
-      </c>
-      <c r="H25" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J25" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K25" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="M25" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="H25" s="0" t="n"/>
+      <c r="K25" s="0" t="n"/>
+      <c r="M25" s="0" t="n"/>
       <c r="N25" s="0" t="n">
-        <v>100003</v>
-      </c>
-      <c r="O25" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P25" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="S25" s="0" t="n"/>
-      <c r="U25" s="0" t="n">
-        <v>2</v>
+        <v>310001</v>
+      </c>
+      <c r="O25" s="0" t="n"/>
+      <c r="P25" s="0" t="n"/>
+      <c r="S25" s="0" t="n">
+        <v>204101</v>
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>204003</v>
+        <v>204002</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
@@ -2370,12 +2365,12 @@
       <c r="C26" s="0" t="n"/>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H26" s="0" t="n">
@@ -2387,7 +2382,7 @@
         </is>
       </c>
       <c r="K26" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M26" s="0" t="n">
         <v>1</v>
@@ -2407,102 +2402,108 @@
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>204101</v>
+        <v>204003</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedChain</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n"/>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M27" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N27" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O27" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P27" s="0" t="n">
-        <v>200008</v>
+        <v>420006</v>
+      </c>
+      <c r="S27" s="0" t="n"/>
+      <c r="U27" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>205001</v>
+        <v>204101</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr"/>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K28" s="0" t="n"/>
       <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="0" t="n">
-        <v>310001</v>
-      </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R28" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>205002</v>
+        <v>205001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingShrink</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="n"/>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr"/>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
@@ -2513,23 +2514,28 @@
         <v>1</v>
       </c>
       <c r="N29" s="0" t="n">
-        <v>100003</v>
+        <v>310001</v>
       </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
-        <v>420006</v>
+        <v>200008</v>
+      </c>
+      <c r="R29" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>205003</v>
+        <v>205002</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
@@ -2539,12 +2545,12 @@
       <c r="C30" s="0" t="n"/>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H30" s="0" t="n">
@@ -2565,121 +2571,109 @@
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>205004</v>
+        <v>205003</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMelee</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeRangedPiercingShrink</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n"/>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
       </c>
       <c r="H31" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="K31" s="0" t="n"/>
       <c r="M31" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="0" t="n">
-        <v>0</v>
+        <v>100003</v>
       </c>
       <c r="O31" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P31" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="S31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="0" t="n">
-        <v>0</v>
+        <v>420006</v>
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>普通近战攻击-单体(兽人战士)</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>206001</v>
+        <v>205004</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeMelee</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H32" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="0" t="n">
-        <v>310001</v>
+        <v>0</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R32" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V32" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>200007</v>
+      </c>
+      <c r="S32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>普通近战攻击-单体(兽人战士)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>210001</v>
+        <v>206001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
@@ -2688,72 +2682,87 @@
       <c r="H33" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K33" s="0" t="n"/>
+      <c r="I33" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M33" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="0" t="n">
         <v>310001</v>
       </c>
       <c r="O33" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>420011</v>
+        <v>200008</v>
       </c>
       <c r="R33" s="0" t="inlineStr">
         <is>
-          <t>type:2&amp;color:1,1,1</t>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V33" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
         </is>
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="n"/>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H34" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I34" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J34" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K34" s="0" t="n">
-        <v>300002</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K34" s="0" t="n"/>
       <c r="M34" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O34" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P34" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T34" s="0" t="n">
-        <v>50</v>
+        <v>420011</v>
+      </c>
+      <c r="R34" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300002</v>
+        <v>300001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -2782,99 +2791,83 @@
         <v>420008</v>
       </c>
       <c r="T35" s="0" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰(敢死队)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300061</v>
+        <v>300002</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G36" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H36" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M36" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N36" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O36" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P36" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R36" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S36" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I37" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M37" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>400003</v>
@@ -2901,13 +2894,13 @@
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
@@ -2929,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>400003</v>
@@ -2956,13 +2949,13 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
@@ -2984,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>400003</v>
@@ -3011,13 +3004,13 @@
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
@@ -3039,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>400003</v>
@@ -3066,13 +3059,13 @@
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -3094,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>400003</v>
@@ -3121,47 +3114,49 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I42" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="K42" s="0" t="n">
-        <v>1700001</v>
-      </c>
       <c r="M42" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O42" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P42" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="0" t="n">
-        <v>0</v>
+      <c r="R42" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S42" s="0" t="n">
         <v>0</v>
@@ -3174,133 +3169,143 @@
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr"/>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr"/>
-      <c r="G43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I43" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.5,0.5</t>
         </is>
       </c>
       <c r="K43" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L43" s="0" t="inlineStr"/>
-      <c r="M43" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>1700001</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N43" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O43" s="0" t="inlineStr"/>
-      <c r="P43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q43" s="0" t="inlineStr"/>
-      <c r="R43" s="0" t="inlineStr"/>
-      <c r="S43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U43" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="O43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
-      </c>
-      <c r="H44" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I44" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J44" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K44" s="0" t="n"/>
-      <c r="L44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="0" t="n"/>
-      <c r="O44" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P44" s="0" t="n">
-        <v>630005</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr"/>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr"/>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L44" s="0" t="inlineStr"/>
+      <c r="M44" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O44" s="0" t="inlineStr"/>
+      <c r="P44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q44" s="0" t="inlineStr"/>
+      <c r="R44" s="0" t="inlineStr"/>
+      <c r="S44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U44" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
@@ -3309,7 +3314,7 @@
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>1000400001:1</t>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H45" s="0" t="n">
@@ -3337,50 +3342,60 @@
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H46" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I46" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K46" s="0" t="n"/>
+      <c r="L46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0" t="n"/>
       <c r="O46" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P46" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H47" s="0" t="n">
@@ -3393,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="0" t="n">
-        <v>500003</v>
+        <v>500001</v>
       </c>
       <c r="O47" s="0" t="n">
         <v>100001</v>
@@ -3403,96 +3418,74 @@
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
+        <v>500002</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="0" t="n">
         <v>500003</v>
       </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeShieldCast</t>
-        </is>
-      </c>
-      <c r="K48" s="0" t="inlineStr">
-        <is>
-          <t>500003</t>
-        </is>
-      </c>
-      <c r="N48" s="0" t="n">
+      <c r="O48" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P48" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="V48" s="0" t="inlineStr">
-        <is>
-          <t>shield_count:3&amp;shield_buff:2000700001</t>
-        </is>
-      </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>500004</v>
+        <v>500003</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeSummon</t>
-        </is>
-      </c>
-      <c r="G49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeShieldCast</t>
+        </is>
       </c>
       <c r="K49" s="0" t="inlineStr">
         <is>
-          <t>500002</t>
-        </is>
-      </c>
-      <c r="M49" s="0" t="n">
-        <v>0</v>
+          <t>500003</t>
+        </is>
       </c>
       <c r="N49" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="O49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="V49" s="0" t="inlineStr">
         <is>
-          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0</t>
+          <t>shield_count:3&amp;shield_buff:2000700001</t>
         </is>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师普攻（自己当前位置召唤1只骷髅战士，5秒一次）</t>
+          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>500005</v>
+        <v>500004</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -3510,7 +3503,7 @@
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>500002</t>
+          <t>1000001</t>
         </is>
       </c>
       <c r="M50" s="0" t="n">
@@ -3525,6 +3518,7 @@
       <c r="P50" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="Q50" s="0" t="inlineStr"/>
       <c r="S50" s="0" t="n">
         <v>0</v>
       </c>
@@ -3536,213 +3530,218 @@
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1</t>
+          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0&amp;summon_offset_x:-0.5</t>
         </is>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师BOSS技能（自己路+上下相邻路每路3只，独立随机骷髅战士/投手，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻）</t>
+          <t>召唤-骷髅召唤师普攻（自己前方0.5召唤1只骷髅战士[随机外貌]，5秒一次，出手特效Effect_Mana_1）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>600001</v>
+        <v>500005</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="0" t="n">
-        <v>500002</v>
+          <t>AttackModeSummon</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="O51" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P51" s="0" t="n">
-        <v>470001</v>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="0" t="inlineStr"/>
+      <c r="S51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="0" t="inlineStr">
+        <is>
+          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1&amp;summon_offset_x:-0.5</t>
+        </is>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>召唤-骷髅召唤师BOSS技能（自己前方0.5,自己路+上下相邻路每路3只，独立随机骷髅战士/投手[随机外貌]，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻，出手特效Effect_Mana_1）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>700001</v>
+        <v>500006</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="n"/>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F52" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
+          <t>AttackModeRegainHPArea</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="I52" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="K52" s="0" t="n">
-        <v>2000001</v>
+        <v>2100002</v>
       </c>
       <c r="M52" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="O52" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P52" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q52" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V52" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
+      </c>
+      <c r="S52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>群体治疗-自身周围5格(牧师技能:治疗同阵营HP不满友军[含自己],治疗量=ATK,经ext100009全局技能挂载,3秒一次)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="n">
-        <v>700002</v>
-      </c>
-      <c r="B53" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C53" s="0" t="n"/>
-      <c r="D53" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
-        </is>
-      </c>
-      <c r="F53" s="0" t="inlineStr">
-        <is>
-          <t>1000600001:0.5</t>
-        </is>
-      </c>
-      <c r="I53" s="0" t="n">
+      <c r="A53" t="n">
+        <v>500007</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AttackModeRegainHPGround</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>11</v>
       </c>
-      <c r="J53" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K53" s="0" t="n">
-        <v>2000002</v>
-      </c>
-      <c r="M53" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O53" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P53" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q53" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V53" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
-      </c>
-      <c r="W53" s="0" t="inlineStr">
-        <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2100003</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>470001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>470001</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>地面持续治疗区域(神官技能:以自身为圆心半径2区域持续5秒,每秒回血=ATK×0.1快照,经ext100010全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>700003</v>
+        <v>600001</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
-        </is>
-      </c>
-      <c r="F54" s="0" t="inlineStr">
-        <is>
-          <t>1000700001:0.5</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J54" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K54" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="M54" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" s="0" t="n">
-        <v>100003</v>
+        <v>500002</v>
       </c>
       <c r="O54" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P54" s="0" t="n">
-        <v>420008</v>
+        <v>470001</v>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>700005</v>
+        <v>700001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
           <t>AttackModeFalluponAreaRandom</t>
         </is>
       </c>
+      <c r="C55" s="0" t="n"/>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall_2</t>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I55" s="0" t="n">
@@ -3752,7 +3751,7 @@
         <v>1.5</v>
       </c>
       <c r="K55" s="0" t="n">
-        <v>200001</v>
+        <v>2000001</v>
       </c>
       <c r="M55" s="0" t="n">
         <v>1.5</v>
@@ -3775,47 +3774,81 @@
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>700006</v>
+        <v>700002</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChainMulti</t>
-        </is>
-      </c>
-      <c r="I56" s="0" t="n"/>
-      <c r="J56" s="0" t="n"/>
-      <c r="K56" s="0" t="n"/>
-      <c r="M56" s="0" t="n"/>
-      <c r="O56" s="0" t="n"/>
-      <c r="P56" s="0" t="n"/>
-      <c r="Q56" s="0" t="n"/>
-      <c r="S56" s="0" t="n">
-        <v>800002</v>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="n"/>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>1000600001:0.5</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P56" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="Q56" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
       </c>
       <c r="V56" s="0" t="inlineStr">
         <is>
-          <t>hit_times:3&amp;hit_interval:0.25</t>
+          <t>gravity:2.4525</t>
         </is>
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>800001</v>
+        <v>700003</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I57" s="0" t="n">
@@ -3824,10 +3857,14 @@
       <c r="J57" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K57" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
+      <c r="K57" s="0" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O57" s="0" t="n">
         <v>100001</v>
@@ -3837,17 +3874,27 @@
       </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>800002</v>
+        <v>700005</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall_2</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I58" s="0" t="n">
@@ -3856,10 +3903,11 @@
       <c r="J58" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="K58" s="0" t="inlineStr">
-        <is>
-          <t>900004&amp;900004</t>
-        </is>
+      <c r="K58" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="M58" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O58" s="0" t="n">
         <v>100001</v>
@@ -3867,117 +3915,119 @@
       <c r="P58" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q58" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V58" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300031</v>
+        <v>700006</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
-      </c>
-      <c r="I59" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J59" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K59" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="0" t="n">
-        <v>420003</v>
-      </c>
+          <t>AttackModeFalluponChainMulti</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="n"/>
+      <c r="J59" s="0" t="n"/>
+      <c r="K59" s="0" t="n"/>
+      <c r="M59" s="0" t="n"/>
+      <c r="O59" s="0" t="n"/>
       <c r="P59" s="0" t="n"/>
-      <c r="U59" s="0" t="n">
-        <v>1</v>
+      <c r="Q59" s="0" t="n"/>
+      <c r="S59" s="0" t="n">
+        <v>800002</v>
+      </c>
+      <c r="V59" s="0" t="inlineStr">
+        <is>
+          <t>hit_times:3&amp;hit_interval:0.25</t>
+        </is>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300032</v>
+        <v>800001</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I60" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K60" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P60" s="0" t="n"/>
-      <c r="U60" s="0" t="n">
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300033</v>
+        <v>800002</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I61" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K61" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P61" s="0" t="n"/>
-      <c r="U61" s="0" t="n">
-        <v>3</v>
+        <v>1.5</v>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
+        <is>
+          <t>900004&amp;900004</t>
+        </is>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300034</v>
+        <v>300031</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
@@ -3988,7 +4038,7 @@
         <v>11</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K62" s="0" t="n">
         <v>900003</v>
@@ -4001,17 +4051,17 @@
       </c>
       <c r="P62" s="0" t="n"/>
       <c r="U62" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300035</v>
+        <v>300032</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -4022,7 +4072,7 @@
         <v>11</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>900003</v>
@@ -4035,191 +4085,140 @@
       </c>
       <c r="P63" s="0" t="n"/>
       <c r="U63" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W63" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300041</v>
+        <v>300033</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E64" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H64" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M64" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N64" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O64" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P64" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R64" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P64" s="0" t="n"/>
+      <c r="U64" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="W64" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300051</v>
+        <v>300034</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="inlineStr"/>
-      <c r="D65" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F65" s="0" t="inlineStr"/>
-      <c r="G65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
       </c>
       <c r="I65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="0" t="inlineStr"/>
-      <c r="K65" s="0" t="inlineStr"/>
-      <c r="L65" s="0" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>900003</v>
+      </c>
       <c r="M65" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N65" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O65" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P65" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="Q65" s="0" t="inlineStr"/>
-      <c r="R65" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>420003</v>
+      </c>
+      <c r="P65" s="0" t="n"/>
       <c r="U65" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W65" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300071</v>
+        <v>300035</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
-      <c r="D66" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G66" s="0" t="n">
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H66" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I66" s="0" t="n">
-        <v>0</v>
+      <c r="J66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R66" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>420003</v>
+      </c>
+      <c r="P66" s="0" t="n"/>
       <c r="U66" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W66" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>207001</v>
+        <v>300041</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
+          <t>AttackModeRangedPiercingRoad</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
         </is>
       </c>
       <c r="H67" s="0" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M67" s="0" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N67" s="0" t="n">
         <v>310001</v>
@@ -4228,14 +4227,167 @@
         <v>100001</v>
       </c>
       <c r="P67" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R67" s="0" t="inlineStr">
+        <is>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
+      </c>
+      <c r="W67" s="0" t="inlineStr">
+        <is>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>300051</v>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr"/>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr"/>
+      <c r="G68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="0" t="inlineStr"/>
+      <c r="K68" s="0" t="inlineStr"/>
+      <c r="L68" s="0" t="inlineStr"/>
+      <c r="M68" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O68" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P68" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="Q68" s="0" t="inlineStr"/>
+      <c r="R68" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="0" t="inlineStr">
+        <is>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R69" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="n">
+        <v>207001</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="0" t="n">
+        <v>310001</v>
+      </c>
+      <c r="O70" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P70" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R67" s="0" t="inlineStr">
+      <c r="R70" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W67" s="0" t="inlineStr">
+      <c r="W70" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -1738,43 +1738,46 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n">
-        <v>102001</v>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="A12" t="n">
+        <v>101007</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" t="n">
         <v>24</v>
       </c>
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>3,1,0.25</t>
-        </is>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>400002</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P12" s="0" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.5,1,1.25</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O12" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P12" t="n">
         <v>200007</v>
       </c>
-      <c r="W12" s="0" t="inlineStr">
-        <is>
-          <t>BOSS技能-向前挥砍攻击前方6格</t>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>勇者普攻-向前挥砍攻击前方3格上中下3排(3x3)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="1">
       <c r="A13" s="0" t="n">
-        <v>102002</v>
+        <v>102001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -1789,7 +1792,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>3,1,1.25</t>
+          <t>3,1,0.25</t>
         </is>
       </c>
       <c r="K13" s="0" t="n">
@@ -1803,103 +1806,96 @@
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-向前挥砍攻击前方6格上中下3排</t>
+          <t>BOSS技能-向前挥砍攻击前方6格</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>102003</v>
+        <v>102002</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstant</t>
-        </is>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeMeleeArea</t>
+        </is>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>3,1,1.25</t>
+        </is>
       </c>
       <c r="K14" s="0" t="n">
-        <v>2100001</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <v>0</v>
+        <v>400002</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="S14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="0" t="n">
-        <v>0</v>
+        <v>200007</v>
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
-          <t>单体瞬时攻击(牧师普攻:瞬间命中无扩散,命中特效Effect_Hit_2)</t>
+          <t>BOSS技能-向前挥砍攻击前方6格上中下3排</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>200001</v>
+        <v>102003</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="n"/>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeInstant</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K15" s="0" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <v>2100001</v>
+      </c>
       <c r="M15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>310001</v>
+        <v>0</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R15" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
+        <v>420008</v>
+      </c>
+      <c r="S15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击</t>
+          <t>单体瞬时攻击(牧师普攻:瞬间命中无扩散,命中特效Effect_Hit_2)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>200002</v>
+        <v>200001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1909,12 +1905,7 @@
       <c r="C16" s="0" t="n"/>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H16" s="0" t="n">
@@ -1924,24 +1915,29 @@
       <c r="M16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="0" t="n">
-        <v>100003</v>
+      <c r="N16" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>420003</v>
+        <v>420011</v>
+      </c>
+      <c r="R16" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击</t>
+          <t>远程攻击-攻击</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="1">
       <c r="A17" s="0" t="n">
-        <v>200003</v>
+        <v>200002</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1951,12 +1947,12 @@
       <c r="C17" s="0" t="n"/>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H17" s="0" t="n">
@@ -1977,13 +1973,13 @@
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-水球直线攻击</t>
+          <t>远程攻击-火球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="1">
       <c r="A18" s="0" t="n">
-        <v>200004</v>
+        <v>200003</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
@@ -1993,12 +1989,12 @@
       <c r="C18" s="0" t="n"/>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedWaterBall</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="H18" s="0" t="n">
@@ -2019,42 +2015,34 @@
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击</t>
+          <t>远程攻击-水球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>201001</v>
+        <v>200004</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedObliqueTracking</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="C19" s="0" t="n"/>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="H19" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="0" t="n">
-        <v>100001</v>
-      </c>
+      <c r="K19" s="0" t="n"/>
       <c r="M19" s="0" t="n">
         <v>1</v>
       </c>
@@ -2065,25 +2053,17 @@
         <v>100001</v>
       </c>
       <c r="P19" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="U19" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="0" t="inlineStr">
-        <is>
-          <t>aim_up:0.5</t>
-        </is>
+        <v>420003</v>
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
+          <t>远程攻击-冰球直线攻击</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>201002</v>
+        <v>201001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
@@ -2093,12 +2073,12 @@
       <c r="C20" s="0" t="n"/>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H20" s="0" t="n">
@@ -2111,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M20" s="0" t="n">
         <v>1</v>
@@ -2135,37 +2115,44 @@
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>201003</v>
+        <v>201002</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
+          <t>AttackModeRangedObliqueTracking</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n"/>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
+          <t>AttackModeVisual_RangedIceBall</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H21" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="I21" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="M21" s="0" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N21" s="0" t="n">
         <v>100003</v>
@@ -2176,15 +2163,23 @@
       <c r="P21" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="0" t="inlineStr">
+        <is>
+          <t>aim_up:0.5</t>
+        </is>
+      </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>201004</v>
+        <v>201003</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
@@ -2193,19 +2188,19 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>1000100001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="H22" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>1.5</v>
@@ -2221,37 +2216,37 @@
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
+          <t>远程攻击-火球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>202001</v>
+        <v>201004</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedTracking</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="n"/>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedLove</t>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>1000100001:0.5</t>
         </is>
       </c>
       <c r="H23" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I23" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="n"/>
+      <c r="K23" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M23" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N23" s="0" t="n">
         <v>100003</v>
@@ -2260,155 +2255,145 @@
         <v>100001</v>
       </c>
       <c r="P23" s="0" t="n">
-        <v>6</v>
+        <v>420006</v>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-跟踪-爱心</t>
+          <t>远程攻击-冰球直线攻击-单体伤害（骷髅）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>203001</v>
+        <v>202001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcArea</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr"/>
+          <t>AttackModeRangedTracking</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n"/>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_RangedLove</t>
+        </is>
       </c>
       <c r="H24" s="0" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="n">
-        <v>1900001</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="0" t="n"/>
       <c r="M24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="0" t="n">
-        <v>100002</v>
+        <v>100003</v>
       </c>
       <c r="O24" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P24" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="R24" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="U24" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
+          <t>远程攻击-跟踪-爱心</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>204001</v>
+        <v>203001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplit</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="n"/>
-      <c r="H25" s="0" t="n"/>
-      <c r="K25" s="0" t="n"/>
-      <c r="M25" s="0" t="n"/>
+          <t>AttackModeRangedArcArea</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr"/>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>1900001</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="N25" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O25" s="0" t="n"/>
-      <c r="P25" s="0" t="n"/>
-      <c r="S25" s="0" t="n">
-        <v>204101</v>
+        <v>100002</v>
+      </c>
+      <c r="O25" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>420011</v>
+      </c>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭</t>
+          <t>远程攻击-抛物线-落点范围(落点AOE,hit_max=5,近者优先;DSP石头+残影拖尾;击中特效1900001;出手sound_knife_miss_2,命中sound_hit_11)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>204002</v>
+        <v>204001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedChain</t>
+          <t>AttackModeRangedSplit</t>
         </is>
       </c>
       <c r="C26" s="0" t="n"/>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
-        </is>
-      </c>
-      <c r="H26" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J26" s="0" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K26" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="M26" s="0" t="n">
-        <v>1</v>
-      </c>
+      <c r="H26" s="0" t="n"/>
+      <c r="K26" s="0" t="n"/>
+      <c r="M26" s="0" t="n"/>
       <c r="N26" s="0" t="n">
-        <v>100003</v>
-      </c>
-      <c r="O26" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P26" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="S26" s="0" t="n"/>
-      <c r="U26" s="0" t="n">
-        <v>2</v>
+        <v>310001</v>
+      </c>
+      <c r="O26" s="0" t="n"/>
+      <c r="P26" s="0" t="n"/>
+      <c r="S26" s="0" t="n">
+        <v>204101</v>
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
+          <t>远程攻击-分裂弓箭</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>204003</v>
+        <v>204002</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
@@ -2418,12 +2403,12 @@
       <c r="C27" s="0" t="n"/>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2435,7 +2420,7 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="M27" s="0" t="n">
         <v>1</v>
@@ -2455,102 +2440,108 @@
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>204101</v>
+        <v>204003</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedSplitChild</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_RangedNormal</t>
+          <t>AttackModeRangedChain</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n"/>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>200001</v>
+      </c>
       <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="N28" s="0" t="n">
+        <v>100003</v>
+      </c>
       <c r="O28" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P28" s="0" t="n">
-        <v>200008</v>
+        <v>420006</v>
+      </c>
+      <c r="S28" s="0" t="n"/>
+      <c r="U28" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-分裂弓箭-子弹道</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>205001</v>
+        <v>204101</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercing</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr"/>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
+          <t>AttackModeRangedSplitChild</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_RangedNormal</t>
         </is>
       </c>
       <c r="H29" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K29" s="0" t="n"/>
       <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="0" t="n">
-        <v>310001</v>
-      </c>
       <c r="O29" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P29" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R29" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-分裂弓箭-子弹道</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>205002</v>
+        <v>205001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingShrink</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="n"/>
+          <t>AttackModeRangedPiercing</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr"/>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>1000500002:0.1</t>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H30" s="0" t="n">
@@ -2561,23 +2552,28 @@
         <v>1</v>
       </c>
       <c r="N30" s="0" t="n">
-        <v>100003</v>
+        <v>310001</v>
       </c>
       <c r="O30" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P30" s="0" t="n">
-        <v>420006</v>
+        <v>200008</v>
+      </c>
+      <c r="R30" s="0" t="inlineStr">
+        <is>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
+          <t>远程攻击-穿透</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>205003</v>
+        <v>205002</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
@@ -2587,12 +2583,12 @@
       <c r="C31" s="0" t="n"/>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedIceBall</t>
+          <t>AttackModeVisual_RangedFireBall</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000500002:0.1</t>
         </is>
       </c>
       <c r="H31" s="0" t="n">
@@ -2613,121 +2609,109 @@
       </c>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>205004</v>
+        <v>205003</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AttackModeMelee</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeRangedPiercingShrink</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n"/>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>1000100002:0.1</t>
+        </is>
       </c>
       <c r="H32" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="K32" s="0" t="n"/>
       <c r="M32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="0" t="n">
-        <v>0</v>
+        <v>100003</v>
       </c>
       <c r="O32" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>200007</v>
-      </c>
-      <c r="S32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="0" t="n">
-        <v>0</v>
+        <v>420006</v>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>普通近战攻击-单体(兽人战士)</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>206001</v>
+        <v>205004</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcTracking</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
+          <t>AttackModeMelee</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H33" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="0" t="n">
-        <v>310001</v>
+        <v>0</v>
       </c>
       <c r="O33" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R33" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="V33" s="0" t="inlineStr">
-        <is>
-          <t>stuck_time:3&amp;stuck_sink:0.1</t>
-        </is>
+        <v>200007</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
+          <t>普通近战攻击-单体(兽人战士)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>210001</v>
+        <v>206001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="n"/>
+          <t>AttackModeRangedArcTracking</t>
+        </is>
+      </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
@@ -2736,72 +2720,87 @@
       <c r="H34" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K34" s="0" t="n"/>
+      <c r="I34" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="M34" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="N34" s="0" t="n">
         <v>310001</v>
       </c>
       <c r="O34" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P34" s="0" t="n">
-        <v>420011</v>
+        <v>200008</v>
       </c>
       <c r="R34" s="0" t="inlineStr">
         <is>
-          <t>type:2&amp;color:1,1,1</t>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
+      </c>
+      <c r="V34" s="0" t="inlineStr">
+        <is>
+          <t>stuck_time:3&amp;stuck_sink:0.1</t>
         </is>
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-攻击-VFX轨迹(白)</t>
+          <t>远程攻击-抛物线-落点跟踪(落点实时跟踪目标,目标死亡则落死亡点,落点范围检测取最近单体命中;collider_area_size第1项=落点检测半径)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>300001</v>
+        <v>210001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>AttackModeExplosion</t>
+          <t>AttackModeRanged</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n"/>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
       <c r="H35" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I35" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J35" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>300002</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="K35" s="0" t="n"/>
       <c r="M35" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>310001</v>
       </c>
       <c r="O35" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P35" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="T35" s="0" t="n">
-        <v>50</v>
+        <v>420011</v>
+      </c>
+      <c r="R35" s="0" t="inlineStr">
+        <is>
+          <t>type:2&amp;color:1,1,1</t>
+        </is>
       </c>
       <c r="W35" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰</t>
+          <t>远程攻击-攻击-VFX轨迹(白)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>300002</v>
+        <v>300001</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2830,99 +2829,83 @@
         <v>420008</v>
       </c>
       <c r="T36" s="0" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
-          <t>爆炸范围攻击-火焰(敢死队)</t>
+          <t>爆炸范围攻击-火焰</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>300061</v>
+        <v>300002</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcBounce</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Axe_1</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeExplosion</t>
+        </is>
       </c>
       <c r="H37" s="0" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>300002</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" s="0" t="n">
-        <v>400003</v>
+        <v>0</v>
       </c>
       <c r="O37" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P37" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R37" s="0" t="inlineStr">
-        <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S37" s="0" t="n">
-        <v>0</v>
+        <v>420008</v>
       </c>
       <c r="T37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
+          <t>爆炸范围攻击-火焰(敢死队)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedRebound</t>
+          <t>AttackModeRangedArcBounce</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Pingpang_1</t>
+          <t>AttackModeVisual_Axe_1</t>
         </is>
       </c>
       <c r="G38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="0" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I38" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M38" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>400003</v>
@@ -2949,13 +2932,13 @@
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
+          <t>跳跳斧-深渊馈赠跳跳斧(分段抛物线弹道,追踪锁定目标,命中后弹跳至附近目标,伤害逐目标减半保底1;collider_area_size第1项=弹跳搜索半径)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
@@ -2977,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="0" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>400003</v>
@@ -3004,13 +2987,13 @@
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
+          <t>回弹菱块Lv1-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持1颗)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
@@ -3032,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>400003</v>
@@ -3059,13 +3042,13 @@
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
+          <t>回弹菱块Lv2-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持2颗)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -3087,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="0" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>400003</v>
@@ -3114,13 +3097,13 @@
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
+          <t>回弹菱块Lv3-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持3颗)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
@@ -3142,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="0" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N42" s="0" t="n">
         <v>400003</v>
@@ -3169,47 +3152,49 @@
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
+          <t>回弹菱块Lv4-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持4颗)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300091</v>
+        <v>300085</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShockwaveRing</t>
+          <t>AttackModeRangedRebound</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Pingpang_1</t>
         </is>
       </c>
       <c r="G43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="0" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I43" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="0" t="inlineStr">
-        <is>
-          <t>0.5,0.5</t>
-        </is>
-      </c>
-      <c r="K43" s="0" t="n">
-        <v>1700001</v>
-      </c>
       <c r="M43" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N43" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O43" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P43" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="O43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="0" t="n">
-        <v>0</v>
+      <c r="R43" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
       </c>
       <c r="S43" s="0" t="n">
         <v>0</v>
@@ -3222,133 +3207,143 @@
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
+          <t>回弹菱块Lv5-深渊馈赠(直线弹道,道路范围内四壁永久反弹±5°随机偏转,同目标1秒命中冷却;永久存活由BUFF每秒维持5颗)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300101</v>
+        <v>300091</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedArcGround</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr"/>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_FireBottle_1</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr"/>
-      <c r="G44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I44" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>AttackModeShockwaveRing</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.5,0.5</t>
         </is>
       </c>
       <c r="K44" s="0" t="n">
-        <v>1800001</v>
-      </c>
-      <c r="L44" s="0" t="inlineStr"/>
-      <c r="M44" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>1700001</v>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N44" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O44" s="0" t="inlineStr"/>
-      <c r="P44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q44" s="0" t="inlineStr"/>
-      <c r="R44" s="0" t="inlineStr"/>
-      <c r="S44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U44" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>420001</v>
+      </c>
+      <c r="O44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
+          <t>第六次冲击-深渊馈赠冲击波(圆环扩张AOE,半径=道路全长+余量0.5,命中击退0.5,伤害由BUFF注入)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>400001</v>
+        <v>300101</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOverlapNoDamage</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t>1000200001:1</t>
-        </is>
-      </c>
-      <c r="H45" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I45" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J45" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K45" s="0" t="n"/>
-      <c r="L45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="0" t="n"/>
-      <c r="O45" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P45" s="0" t="n">
-        <v>630005</v>
+          <t>AttackModeRangedArcGround</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr"/>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_FireBottle_1</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr"/>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="L45" s="0" t="inlineStr"/>
+      <c r="M45" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>400003</v>
+      </c>
+      <c r="O45" s="0" t="inlineStr"/>
+      <c r="P45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q45" s="0" t="inlineStr"/>
+      <c r="R45" s="0" t="inlineStr"/>
+      <c r="S45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U45" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-粘液减速</t>
+          <t>瓶装炼狱火-深渊馈赠(抛物线火瓶:飞向固定落点不追踪,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒;collider_area_size第1项=燃烧半径)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>1000400001:1</t>
+          <t>1000200001:1</t>
         </is>
       </c>
       <c r="H46" s="0" t="n">
@@ -3385,50 +3380,60 @@
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
-          <t>重叠攻击-中毒</t>
+          <t>重叠攻击-粘液减速</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>500001</v>
+        <v>400002</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeOverlapNoDamage</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>1000400001:1</t>
         </is>
       </c>
       <c r="H47" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="0" t="n">
-        <v>500001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K47" s="0" t="n"/>
+      <c r="L47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0" t="n"/>
       <c r="O47" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P47" s="0" t="n">
-        <v>470001</v>
+        <v>630005</v>
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>重叠攻击-中毒</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
+          <t>AttackModeRegainHP</t>
         </is>
       </c>
       <c r="H48" s="0" t="n">
@@ -3441,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="0" t="n">
-        <v>500003</v>
+        <v>500001</v>
       </c>
       <c r="O48" s="0" t="n">
         <v>100001</v>
@@ -3451,97 +3456,74 @@
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>加血</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
+        <v>500002</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRegainDR</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="0" t="n">
         <v>500003</v>
       </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeShieldCast</t>
-        </is>
-      </c>
-      <c r="K49" s="0" t="inlineStr">
-        <is>
-          <t>500003</t>
-        </is>
-      </c>
-      <c r="N49" s="0" t="n">
+      <c r="O49" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P49" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="V49" s="0" t="inlineStr">
-        <is>
-          <t>shield_count:3&amp;shield_buff:2000700001</t>
-        </is>
-      </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
+          <t>加护甲</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>500004</v>
+        <v>500003</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeSummon</t>
-        </is>
-      </c>
-      <c r="G50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeShieldCast</t>
+        </is>
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>1000001</t>
-        </is>
-      </c>
-      <c r="M50" s="0" t="n">
-        <v>0</v>
+          <t>500003</t>
+        </is>
       </c>
       <c r="N50" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="O50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="0" t="inlineStr"/>
-      <c r="S50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0&amp;summon_offset_x:-0.5</t>
+          <t>shield_count:3&amp;shield_buff:2000700001</t>
         </is>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师普攻（自己前方0.5召唤1只骷髅战士[随机外貌]，5秒一次，出手特效Effect_Mana_1）</t>
+          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>500005</v>
+        <v>500004</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3586,22 +3568,22 @@
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
-          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1&amp;summon_offset_x:-0.5</t>
+          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0&amp;summon_offset_x:-0.5</t>
         </is>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师BOSS技能（自己前方0.5,自己路+上下相邻路每路3只，独立随机骷髅战士/投手[随机外貌]，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻，出手特效Effect_Mana_1）</t>
+          <t>召唤-骷髅召唤师普攻（自己前方0.5召唤1只骷髅战士[随机外貌]，5秒一次，出手特效Effect_Mana_1）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>500006</v>
+        <v>500005</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHPArea</t>
+          <t>AttackModeSummon</t>
         </is>
       </c>
       <c r="G52" s="0" t="n">
@@ -3611,13 +3593,12 @@
         <v>0</v>
       </c>
       <c r="I52" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J52" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K52" s="0" t="n">
-        <v>2100002</v>
+        <v>0</v>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
       </c>
       <c r="M52" s="0" t="n">
         <v>0</v>
@@ -3629,158 +3610,161 @@
         <v>0</v>
       </c>
       <c r="P52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="0" t="inlineStr"/>
+      <c r="S52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1&amp;summon_offset_x:-0.5</t>
+        </is>
+      </c>
+      <c r="W52" s="0" t="inlineStr">
+        <is>
+          <t>召唤-骷髅召唤师BOSS技能（自己前方0.5,自己路+上下相邻路每路3只，独立随机骷髅战士/投手[随机外貌]，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻，出手特效Effect_Mana_1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
+        <v>500006</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeRegainHPArea</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>2100002</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="S52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="0" t="inlineStr">
+      <c r="O53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="0" t="n">
+        <v>470001</v>
+      </c>
+      <c r="S53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
         <is>
           <t>群体治疗-自身周围5格(牧师技能:治疗同阵营HP不满友军[含自己],治疗量=ATK,经ext100009全局技能挂载,3秒一次)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>500007</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>AttackModeRegainHPGround</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>11</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2100003</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>470001</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>470001</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>地面持续治疗区域(神官技能:以自身为圆心半径2区域持续5秒,每秒回血=ATK×0.1快照,经ext100010全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>600001</v>
+        <v>500007</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeRegainHPGround</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" s="0" t="n">
-        <v>500002</v>
+        <v>2100003</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="0" t="n">
+        <v>470001</v>
       </c>
       <c r="O54" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P54" s="0" t="n">
         <v>470001</v>
       </c>
+      <c r="S54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>地面持续治疗区域(神官技能:以自身为圆心半径2区域持续5秒,每秒回血=ATK×0.1快照,经ext100010全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="n"/>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
-        </is>
-      </c>
-      <c r="F55" s="0" t="inlineStr">
-        <is>
-          <t>1000500001:0.5</t>
-        </is>
-      </c>
-      <c r="I55" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J55" s="0" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K55" s="0" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="M55" s="0" t="n">
-        <v>1.5</v>
+        <v>500002</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q55" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V55" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
+        <v>470001</v>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>700002</v>
+        <v>700001</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -3790,12 +3774,12 @@
       <c r="C56" s="0" t="n"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
+          <t>AttackModeVisual_RangedFireBall_2</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000500001:0.5</t>
         </is>
       </c>
       <c r="I56" s="0" t="n">
@@ -3805,7 +3789,7 @@
         <v>1.5</v>
       </c>
       <c r="K56" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="M56" s="0" t="n">
         <v>1.5</v>
@@ -3828,27 +3812,28 @@
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>700003</v>
+        <v>700002</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="n"/>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>1000700001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I57" s="0" t="n">
@@ -3858,13 +3843,10 @@
         <v>1.5</v>
       </c>
       <c r="K57" s="0" t="n">
-        <v>800001</v>
+        <v>2000002</v>
       </c>
       <c r="M57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O57" s="0" t="n">
         <v>100001</v>
@@ -3872,24 +3854,34 @@
       <c r="P57" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q57" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V57" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>700005</v>
+        <v>700003</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="D58" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall_2</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
@@ -3904,10 +3896,13 @@
         <v>1.5</v>
       </c>
       <c r="K58" s="0" t="n">
-        <v>200001</v>
+        <v>800001</v>
       </c>
       <c r="M58" s="0" t="n">
-        <v>1.5</v>
+        <v>3</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O58" s="0" t="n">
         <v>100001</v>
@@ -3915,87 +3910,98 @@
       <c r="P58" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="Q58" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V58" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
-      </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>700006</v>
+        <v>700005</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChainMulti</t>
-        </is>
-      </c>
-      <c r="I59" s="0" t="n"/>
-      <c r="J59" s="0" t="n"/>
-      <c r="K59" s="0" t="n"/>
-      <c r="M59" s="0" t="n"/>
-      <c r="O59" s="0" t="n"/>
-      <c r="P59" s="0" t="n"/>
-      <c r="Q59" s="0" t="n"/>
-      <c r="S59" s="0" t="n">
-        <v>800002</v>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall_2</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>1000700001:0.5</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="M59" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>420008</v>
+      </c>
+      <c r="Q59" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
       </c>
       <c r="V59" s="0" t="inlineStr">
         <is>
-          <t>hit_times:3&amp;hit_interval:0.25</t>
+          <t>gravity:2.4525</t>
         </is>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>800001</v>
+        <v>700006</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
-        </is>
-      </c>
-      <c r="I60" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J60" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K60" s="0" t="inlineStr">
-        <is>
-          <t>900001&amp;900002</t>
-        </is>
-      </c>
-      <c r="O60" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P60" s="0" t="n">
-        <v>420008</v>
+          <t>AttackModeFalluponChainMulti</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="n"/>
+      <c r="J60" s="0" t="n"/>
+      <c r="K60" s="0" t="n"/>
+      <c r="M60" s="0" t="n"/>
+      <c r="O60" s="0" t="n"/>
+      <c r="P60" s="0" t="n"/>
+      <c r="Q60" s="0" t="n"/>
+      <c r="S60" s="0" t="n">
+        <v>800002</v>
+      </c>
+      <c r="V60" s="0" t="inlineStr">
+        <is>
+          <t>hit_times:3&amp;hit_interval:0.25</t>
+        </is>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -4010,7 +4016,7 @@
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>900004&amp;900004</t>
+          <t>900001&amp;900002</t>
         </is>
       </c>
       <c r="O61" s="0" t="n">
@@ -4021,47 +4027,45 @@
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300031</v>
+        <v>800002</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
+          <t>AttackModeFalluponChain</t>
         </is>
       </c>
       <c r="I62" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K62" s="0" t="n">
-        <v>900003</v>
-      </c>
-      <c r="M62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P62" s="0" t="n"/>
-      <c r="U62" s="0" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
+        <is>
+          <t>900004&amp;900004</t>
+        </is>
+      </c>
+      <c r="O62" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -4072,7 +4076,7 @@
         <v>11</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>900003</v>
@@ -4085,17 +4089,17 @@
       </c>
       <c r="P63" s="0" t="n"/>
       <c r="U63" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W63" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -4106,7 +4110,7 @@
         <v>11</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>900003</v>
@@ -4119,17 +4123,17 @@
       </c>
       <c r="P64" s="0" t="n"/>
       <c r="U64" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W64" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -4140,7 +4144,7 @@
         <v>11</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>900003</v>
@@ -4153,17 +4157,17 @@
       </c>
       <c r="P65" s="0" t="n"/>
       <c r="U65" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W65" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -4174,7 +4178,7 @@
         <v>11</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>900003</v>
@@ -4187,92 +4191,75 @@
       </c>
       <c r="P66" s="0" t="n"/>
       <c r="U66" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W66" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300041</v>
+        <v>300035</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
-      </c>
-      <c r="H67" s="0" t="n">
-        <v>0.3</v>
+          <t>AttackModeInstantAreaThunder</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="0" t="n">
+        <v>900003</v>
       </c>
       <c r="M67" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N67" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O67" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P67" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="R67" s="0" t="inlineStr">
-        <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+        <v>420003</v>
+      </c>
+      <c r="P67" s="0" t="n"/>
+      <c r="U67" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="W67" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300051</v>
+        <v>300041</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr"/>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F68" s="0" t="inlineStr"/>
-      <c r="G68" s="0" t="n">
-        <v>0</v>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
       </c>
       <c r="H68" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="I68" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="0" t="inlineStr"/>
-      <c r="K68" s="0" t="inlineStr"/>
-      <c r="L68" s="0" t="inlineStr"/>
       <c r="M68" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N68" s="0" t="n">
-        <v>400003</v>
+        <v>310001</v>
       </c>
       <c r="O68" s="0" t="n">
         <v>100001</v>
@@ -4280,43 +4267,35 @@
       <c r="P68" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q68" s="0" t="inlineStr"/>
       <c r="R68" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S68" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="0" t="n">
-        <v>0</v>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W68" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr"/>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr"/>
       <c r="G69" s="0" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H69" s="0" t="n">
         <v>0.3</v>
@@ -4324,15 +4303,22 @@
       <c r="I69" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="J69" s="0" t="inlineStr"/>
+      <c r="K69" s="0" t="inlineStr"/>
+      <c r="L69" s="0" t="inlineStr"/>
       <c r="M69" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N69" s="0" t="n">
-        <v>0</v>
+        <v>400003</v>
+      </c>
+      <c r="O69" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P69" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q69" s="0" t="inlineStr"/>
       <c r="R69" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -4349,51 +4335,102 @@
       </c>
       <c r="W69" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
+        <v>300071</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R70" s="0" t="inlineStr">
+        <is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="0" t="inlineStr">
+        <is>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="12" customHeight="1" s="1">
+      <c r="A71" s="0" t="n">
         <v>207001</v>
       </c>
-      <c r="B70" s="0" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>AttackModeRanged</t>
         </is>
       </c>
-      <c r="D70" s="0" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>AttackModeVisual_RangedNormal</t>
         </is>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H71" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M70" s="0" t="n">
+      <c r="M71" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N70" s="0" t="n">
+      <c r="N71" s="0" t="n">
         <v>310001</v>
       </c>
-      <c r="O70" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P70" s="0" t="n">
+      <c r="O71" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P71" s="0" t="n">
         <v>200008</v>
       </c>
-      <c r="R70" s="0" t="inlineStr">
+      <c r="R71" s="0" t="inlineStr">
         <is>
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
-      <c r="W70" s="0" t="inlineStr">
+      <c r="W71" s="0" t="inlineStr">
         <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="12" customHeight="1" s="1"/>
     <row r="72" ht="12" customHeight="1" s="1"/>
     <row r="73" ht="12" customHeight="1" s="1"/>
     <row r="74" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1738,38 +1738,38 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>101007</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>AttackModeMeleeArea</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>1.5,1,1.25</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="0" t="n">
         <v>400003</v>
       </c>
-      <c r="O12" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="O12" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P12" s="0" t="n">
         <v>200007</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="U12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="0" t="inlineStr">
         <is>
           <t>勇者普攻-向前挥砍攻击前方3格上中下3排(3x3)</t>
         </is>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>400003</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>400003</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>400003</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="0" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="N42" s="0" t="n">
         <v>400003</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N43" s="0" t="n">
         <v>400003</v>
@@ -3313,10 +3313,8 @@
         <v>400003</v>
       </c>
       <c r="O45" s="0" t="inlineStr"/>
-      <c r="P45" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P45" s="0" t="n">
+        <v>420006</v>
       </c>
       <c r="Q45" s="0" t="inlineStr"/>
       <c r="R45" s="0" t="inlineStr"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33" customWidth="1" style="1" min="2" max="2"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHP</t>
+          <t>AttackModeRegainHPAndDR</t>
         </is>
       </c>
       <c r="H48" s="0" t="n">
@@ -3454,74 +3454,97 @@
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
-          <t>加血</t>
+          <t>加血加护甲</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>500002</v>
+        <v>500003</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainDR</t>
-        </is>
-      </c>
-      <c r="H49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="0" t="n">
-        <v>500003</v>
-      </c>
-      <c r="O49" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P49" s="0" t="n">
+          <t>AttackModeShieldCast</t>
+        </is>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>500003</t>
+        </is>
+      </c>
+      <c r="N49" s="0" t="n">
         <v>470001</v>
       </c>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>shield_count:3&amp;shield_buff:2000700001</t>
+        </is>
+      </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>加护甲</t>
+          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>500003</v>
+        <v>500004</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>AttackModeShieldCast</t>
-        </is>
+          <t>AttackModeSummon</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>500003</t>
-        </is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="N50" s="0" t="n">
         <v>470001</v>
       </c>
+      <c r="O50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="0" t="inlineStr"/>
+      <c r="S50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t>shield_count:3&amp;shield_buff:2000700001</t>
+          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0&amp;summon_offset_x:-0.5</t>
         </is>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
-          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
+          <t>召唤-骷髅召唤师普攻（自己前方0.5召唤1只骷髅战士[随机外貌]，5秒一次，出手特效Effect_Mana_1）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>500004</v>
+        <v>500005</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -3566,22 +3589,22 @@
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
-          <t>summon_npc_ids:20010001&amp;summon_count:1&amp;road_spread:0&amp;summon_offset_x:-0.5</t>
+          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1&amp;summon_offset_x:-0.5</t>
         </is>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师普攻（自己前方0.5召唤1只骷髅战士[随机外貌]，5秒一次，出手特效Effect_Mana_1）</t>
+          <t>召唤-骷髅召唤师BOSS技能（自己前方0.5,自己路+上下相邻路每路3只，独立随机骷髅战士/投手[随机外貌]，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻，出手特效Effect_Mana_1）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>500005</v>
+        <v>500006</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>AttackModeSummon</t>
+          <t>AttackModeRegainHPArea</t>
         </is>
       </c>
       <c r="G52" s="0" t="n">
@@ -3591,12 +3614,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="0" t="inlineStr">
-        <is>
-          <t>1000001</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>2100002</v>
       </c>
       <c r="M52" s="0" t="n">
         <v>0</v>
@@ -3608,9 +3632,8 @@
         <v>0</v>
       </c>
       <c r="P52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="0" t="inlineStr"/>
+        <v>470001</v>
+      </c>
       <c r="S52" s="0" t="n">
         <v>0</v>
       </c>
@@ -3620,24 +3643,19 @@
       <c r="U52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="0" t="inlineStr">
-        <is>
-          <t>summon_npc_ids:20010001,20020001&amp;summon_count:3&amp;road_spread:1&amp;summon_offset_x:-0.5</t>
-        </is>
-      </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
-          <t>召唤-骷髅召唤师BOSS技能（自己前方0.5,自己路+上下相邻路每路3只，独立随机骷髅战士/投手[随机外貌]，共最多9只，越界自然衰减；ext100008攻击意图内30秒一发顶替普攻，出手特效Effect_Mana_1）</t>
+          <t>群体治疗-自身周围5格(牧师技能:治疗同阵营HP不满友军[含自己],治疗量=ATK,经ext100009全局技能挂载,3秒一次)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>500006</v>
+        <v>500007</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHPArea</t>
+          <t>AttackModeRegainHPGround</t>
         </is>
       </c>
       <c r="G53" s="0" t="n">
@@ -3650,10 +3668,10 @@
         <v>11</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>2100002</v>
+        <v>2100003</v>
       </c>
       <c r="M53" s="0" t="n">
         <v>0</v>
@@ -3671,98 +3689,101 @@
         <v>0</v>
       </c>
       <c r="T53" s="0" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
-          <t>群体治疗-自身周围5格(牧师技能:治疗同阵营HP不满友军[含自己],治疗量=ATK,经ext100009全局技能挂载,3秒一次)</t>
+          <t>地面持续治疗区域(神官技能:以自身为圆心半径2区域持续5秒,每秒回血=ATK×0.1快照,经ext100010全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>500007</v>
+        <v>600001</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRegainHPGround</t>
-        </is>
-      </c>
-      <c r="G54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeLure</t>
+        </is>
       </c>
       <c r="J54" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54" s="0" t="n">
-        <v>2100003</v>
-      </c>
-      <c r="M54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="0" t="n">
-        <v>470001</v>
+        <v>500002</v>
       </c>
       <c r="O54" s="0" t="n">
-        <v>0</v>
+        <v>100001</v>
       </c>
       <c r="P54" s="0" t="n">
         <v>470001</v>
       </c>
-      <c r="S54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U54" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
-          <t>地面持续治疗区域(神官技能:以自身为圆心半径2区域持续5秒,每秒回血=ATK×0.1快照,经ext100010全局技能挂载,10秒一次)</t>
+          <t>引诱敌人到当前线路</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>600001</v>
+        <v>700001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AttackModeLure</t>
-        </is>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="n"/>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedFireBall_2</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>1000500001:0.5</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K55" s="0" t="n">
-        <v>500002</v>
+        <v>2000001</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>1.5</v>
       </c>
       <c r="O55" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>470001</v>
+        <v>420008</v>
+      </c>
+      <c r="Q55" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V55" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
-          <t>引诱敌人到当前线路</t>
+          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>700001</v>
+        <v>700002</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -3772,12 +3793,12 @@
       <c r="C56" s="0" t="n"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_RangedFireBall_2</t>
+          <t>AttackModeVisual_RangedWaterBall_2</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>1000500001:0.5</t>
+          <t>1000600001:0.5</t>
         </is>
       </c>
       <c r="I56" s="0" t="n">
@@ -3787,7 +3808,7 @@
         <v>1.5</v>
       </c>
       <c r="K56" s="0" t="n">
-        <v>2000001</v>
+        <v>2000002</v>
       </c>
       <c r="M56" s="0" t="n">
         <v>1.5</v>
@@ -3810,28 +3831,27 @@
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-火球-随机落点(火大魔法师BOSS技能)</t>
+          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>700002</v>
+        <v>700003</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="n"/>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedWaterBall_2</t>
+          <t>AttackModeFalluponArea</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>AttackMode_Fallupon_Ice_1</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>1000600001:0.5</t>
+          <t>1000700001:0.5</t>
         </is>
       </c>
       <c r="I57" s="0" t="n">
@@ -3841,10 +3861,13 @@
         <v>1.5</v>
       </c>
       <c r="K57" s="0" t="n">
-        <v>2000002</v>
+        <v>800001</v>
       </c>
       <c r="M57" s="0" t="n">
-        <v>1.5</v>
+        <v>3</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>100003</v>
       </c>
       <c r="O57" s="0" t="n">
         <v>100001</v>
@@ -3852,34 +3875,24 @@
       <c r="P57" s="0" t="n">
         <v>420008</v>
       </c>
-      <c r="Q57" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
-      </c>
-      <c r="V57" s="0" t="inlineStr">
-        <is>
-          <t>gravity:2.4525</t>
-        </is>
-      </c>
       <c r="W57" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-水球-随机落点(水大魔法师BOSS技能)</t>
+          <t>下落范围攻击-冰球</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>700003</v>
+        <v>700005</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponArea</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>AttackMode_Fallupon_Ice_1</t>
+          <t>AttackModeFalluponAreaRandom</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_RangedIceBall_2</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
@@ -3894,13 +3907,10 @@
         <v>1.5</v>
       </c>
       <c r="K58" s="0" t="n">
-        <v>800001</v>
+        <v>200001</v>
       </c>
       <c r="M58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" s="0" t="n">
-        <v>100003</v>
+        <v>1.5</v>
       </c>
       <c r="O58" s="0" t="n">
         <v>100001</v>
@@ -3908,98 +3918,87 @@
       <c r="P58" s="0" t="n">
         <v>420008</v>
       </c>
+      <c r="Q58" s="0" t="inlineStr">
+        <is>
+          <t>0,6,0</t>
+        </is>
+      </c>
+      <c r="V58" s="0" t="inlineStr">
+        <is>
+          <t>gravity:2.4525</t>
+        </is>
+      </c>
       <c r="W58" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球</t>
+          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>700005</v>
+        <v>700006</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponAreaRandom</t>
-        </is>
-      </c>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedIceBall_2</t>
-        </is>
-      </c>
-      <c r="F59" s="0" t="inlineStr">
-        <is>
-          <t>1000700001:0.5</t>
-        </is>
-      </c>
-      <c r="I59" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J59" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K59" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="M59" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O59" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P59" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="Q59" s="0" t="inlineStr">
-        <is>
-          <t>0,6,0</t>
-        </is>
+          <t>AttackModeFalluponChainMulti</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="n"/>
+      <c r="J59" s="0" t="n"/>
+      <c r="K59" s="0" t="n"/>
+      <c r="M59" s="0" t="n"/>
+      <c r="O59" s="0" t="n"/>
+      <c r="P59" s="0" t="n"/>
+      <c r="Q59" s="0" t="n"/>
+      <c r="S59" s="0" t="n">
+        <v>800002</v>
       </c>
       <c r="V59" s="0" t="inlineStr">
         <is>
-          <t>gravity:2.4525</t>
+          <t>hit_times:3&amp;hit_interval:0.25</t>
         </is>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
-          <t>下落范围攻击-冰球-随机落点(冰大魔法师BOSS技能)</t>
+          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>700006</v>
+        <v>800001</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChainMulti</t>
-        </is>
-      </c>
-      <c r="I60" s="0" t="n"/>
-      <c r="J60" s="0" t="n"/>
-      <c r="K60" s="0" t="n"/>
-      <c r="M60" s="0" t="n"/>
-      <c r="O60" s="0" t="n"/>
-      <c r="P60" s="0" t="n"/>
-      <c r="Q60" s="0" t="n"/>
-      <c r="S60" s="0" t="n">
-        <v>800002</v>
-      </c>
-      <c r="V60" s="0" t="inlineStr">
-        <is>
-          <t>hit_times:3&amp;hit_interval:0.25</t>
-        </is>
+          <t>AttackModeFalluponChain</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
+        <is>
+          <t>900001&amp;900002</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>420008</v>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
-          <t>天降连锁-三连发发射器(0.5秒内发3次800002BOSS雷击,每发独立随机落点;雷大魔法师BOSS技能)</t>
+          <t>下落攻击-雷击</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>800001</v>
+        <v>800002</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -4014,7 +4013,7 @@
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>900001&amp;900002</t>
+          <t>900004&amp;900004</t>
         </is>
       </c>
       <c r="O61" s="0" t="n">
@@ -4025,45 +4024,47 @@
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击</t>
+          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>800002</v>
+        <v>300031</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>AttackModeFalluponChain</t>
+          <t>AttackModeInstantAreaThunder</t>
         </is>
       </c>
       <c r="I62" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K62" s="0" t="inlineStr">
-        <is>
-          <t>900004&amp;900004</t>
-        </is>
-      </c>
-      <c r="O62" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P62" s="0" t="n">
-        <v>420008</v>
+        <v>0.2</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>900003</v>
+      </c>
+      <c r="M62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="0" t="n">
+        <v>420003</v>
+      </c>
+      <c r="P62" s="0" t="n"/>
+      <c r="U62" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="W62" s="0" t="inlineStr">
         <is>
-          <t>下落攻击-雷击-BOSS(雷大魔法师BOSS技能子雷,特效Effect_Thunder_4)</t>
+          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300031</v>
+        <v>300032</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -4074,7 +4075,7 @@
         <v>11</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>900003</v>
@@ -4087,17 +4088,17 @@
       </c>
       <c r="P63" s="0" t="n"/>
       <c r="U63" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv1(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300032</v>
+        <v>300033</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -4108,7 +4109,7 @@
         <v>11</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>900003</v>
@@ -4121,17 +4122,17 @@
       </c>
       <c r="P64" s="0" t="n"/>
       <c r="U64" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv2(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300033</v>
+        <v>300034</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -4142,7 +4143,7 @@
         <v>11</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>900003</v>
@@ -4155,17 +4156,17 @@
       </c>
       <c r="P65" s="0" t="n"/>
       <c r="U65" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W65" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv3(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300034</v>
+        <v>300035</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -4176,7 +4177,7 @@
         <v>11</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>900003</v>
@@ -4189,75 +4190,92 @@
       </c>
       <c r="P66" s="0" t="n"/>
       <c r="U66" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W66" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv4(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300035</v>
+        <v>300041</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>AttackModeInstantAreaThunder</t>
-        </is>
-      </c>
-      <c r="I67" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="J67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="0" t="n">
-        <v>900003</v>
+          <t>AttackModeRangedPiercingRoad</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>AttackModeVisual_Minecart_1</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>0.3</v>
       </c>
       <c r="M67" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N67" s="0" t="n">
-        <v>420003</v>
-      </c>
-      <c r="P67" s="0" t="n"/>
-      <c r="U67" s="0" t="n">
-        <v>5</v>
+        <v>310001</v>
+      </c>
+      <c r="O67" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="P67" s="0" t="n">
+        <v>420001</v>
+      </c>
+      <c r="R67" s="0" t="inlineStr">
+        <is>
+          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
+        </is>
       </c>
       <c r="W67" s="0" t="inlineStr">
         <is>
-          <t>落雷-深渊馈赠闪电Lv5(瞬时落点AOE,半径/单雷命中上限随级)</t>
+          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300041</v>
+        <v>300051</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedPiercingRoad</t>
-        </is>
-      </c>
+          <t>AttackModeRangedBoomerang</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr"/>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Minecart_1</t>
-        </is>
-      </c>
-      <c r="E68" s="0" t="inlineStr">
-        <is>
-          <t>ambient:sh&amp;cast:1&amp;receive:1</t>
-        </is>
+          <t>AttackModeVisual_Boomerang_1</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr"/>
+      <c r="G68" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H68" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="I68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="0" t="inlineStr"/>
+      <c r="K68" s="0" t="inlineStr"/>
+      <c r="L68" s="0" t="inlineStr"/>
       <c r="M68" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N68" s="0" t="n">
-        <v>310001</v>
+        <v>400003</v>
       </c>
       <c r="O68" s="0" t="n">
         <v>100001</v>
@@ -4265,35 +4283,43 @@
       <c r="P68" s="0" t="n">
         <v>420001</v>
       </c>
+      <c r="Q68" s="0" t="inlineStr"/>
       <c r="R68" s="0" t="inlineStr">
         <is>
-          <t>count:12&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05&amp;shrink:0.05</t>
-        </is>
+          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
+        </is>
+      </c>
+      <c r="S68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="W68" s="0" t="inlineStr">
         <is>
-          <t>矿车-深渊馈赠失控的矿车(沿路从左向右碾压,穿透整路,伤害逐目标减半,到路尽头销毁)</t>
+          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300051</v>
+        <v>300071</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>AttackModeRangedBoomerang</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr"/>
+          <t>AttackModeOrbit</t>
+        </is>
+      </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Boomerang_1</t>
-        </is>
-      </c>
-      <c r="F69" s="0" t="inlineStr"/>
+          <t>AttackModeVisual_Book_1</t>
+        </is>
+      </c>
       <c r="G69" s="0" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H69" s="0" t="n">
         <v>0.3</v>
@@ -4301,22 +4327,15 @@
       <c r="I69" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="0" t="inlineStr"/>
-      <c r="K69" s="0" t="inlineStr"/>
-      <c r="L69" s="0" t="inlineStr"/>
       <c r="M69" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N69" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="O69" s="0" t="n">
-        <v>100001</v>
+        <v>0</v>
       </c>
       <c r="P69" s="0" t="n">
         <v>420001</v>
       </c>
-      <c r="Q69" s="0" t="inlineStr"/>
       <c r="R69" s="0" t="inlineStr">
         <is>
           <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
@@ -4333,102 +4352,51 @@
       </c>
       <c r="W69" s="0" t="inlineStr">
         <is>
-          <t>回旋镖-深渊馈赠死亡回旋(三段式飞行,伤害逐目标减半保底1)</t>
+          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300071</v>
+        <v>207001</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>AttackModeOrbit</t>
+          <t>AttackModeRanged</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>AttackModeVisual_Book_1</t>
-        </is>
-      </c>
-      <c r="G70" s="0" t="n">
-        <v>11</v>
+          <t>AttackModeVisual_RangedNormal</t>
+        </is>
       </c>
       <c r="H70" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I70" s="0" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M70" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" s="0" t="n">
-        <v>0</v>
+        <v>310001</v>
+      </c>
+      <c r="O70" s="0" t="n">
+        <v>100001</v>
       </c>
       <c r="P70" s="0" t="n">
-        <v>420001</v>
+        <v>200008</v>
       </c>
       <c r="R70" s="0" t="inlineStr">
         <is>
-          <t>count:8&amp;interval:0.05&amp;startAlpha:0.4&amp;endAlpha:0.02</t>
-        </is>
-      </c>
-      <c r="S70" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="0" t="n">
-        <v>0</v>
+          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
+        </is>
       </c>
       <c r="W70" s="0" t="inlineStr">
         <is>
-          <t>知识的力量-深渊馈赠(环绕最前排魔物旋转的书本,常驻不自毁,触碰敌人造成魔王攻击力40%伤害,每只书对同一敌人0.5秒冷却)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="12" customHeight="1" s="1">
-      <c r="A71" s="0" t="n">
-        <v>207001</v>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeRanged</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="inlineStr">
-        <is>
-          <t>AttackModeVisual_RangedNormal</t>
-        </is>
-      </c>
-      <c r="H71" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" s="0" t="n">
-        <v>310001</v>
-      </c>
-      <c r="O71" s="0" t="n">
-        <v>100001</v>
-      </c>
-      <c r="P71" s="0" t="n">
-        <v>200008</v>
-      </c>
-      <c r="R71" s="0" t="inlineStr">
-        <is>
-          <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
-        </is>
-      </c>
-      <c r="W71" s="0" t="inlineStr">
-        <is>
           <t>远程攻击-攻击(人类弓手)</t>
         </is>
       </c>
     </row>
+    <row r="71" ht="12" customHeight="1" s="1"/>
     <row r="72" ht="12" customHeight="1" s="1"/>
     <row r="73" ht="12" customHeight="1" s="1"/>
     <row r="74" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000500002:0.25</t>
         </is>
       </c>
       <c r="I8" s="0" t="n">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
-          <t>远程瞬时-捶地火锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%烧伤）</t>
+          <t>远程瞬时-捶地火锥（目标脚下释放，范围命中最多3个，护甲双倍/血量半伤，25%烧伤）</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000100002:0.25</t>
         </is>
       </c>
       <c r="I9" s="0" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="W9" s="0" t="inlineStr">
         <is>
-          <t>远程瞬时-捶地冰锥（目标脚下释放，最多命中5个全额，护甲双倍/血量半伤，10%冰缓）</t>
+          <t>远程瞬时-捶地冰锥（目标脚下释放，范围命中最多3个，护甲双倍/血量半伤，25%冰缓）</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000500002:0.25</t>
         </is>
       </c>
       <c r="H20" s="0" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%烧伤）</t>
+          <t>远程攻击-火球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,25%烧伤）</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000100002:0.25</t>
         </is>
       </c>
       <c r="H21" s="0" t="n">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,10%冰减速）</t>
+          <t>远程攻击-冰球直线斜射跟踪-范围伤害（人类,离爆炸点最近3个,25%冰减速）</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000500002:0.25</t>
         </is>
       </c>
       <c r="H27" s="0" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，10%烧伤）</t>
+          <t>远程攻击-连锁火球（直线追踪，连锁2次共3目标，25%烧伤）</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000100002:0.25</t>
         </is>
       </c>
       <c r="H28" s="0" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，10%冰减速）</t>
+          <t>远程攻击-连锁冰球（直线追踪，连锁2次共3目标，25%冰减速）</t>
         </is>
       </c>
     </row>
@@ -2565,9 +2565,12 @@
           <t>count:6&amp;interval:0.05&amp;startAlpha:0.5&amp;endAlpha:0.05</t>
         </is>
       </c>
+      <c r="U30" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透</t>
+          <t>远程攻击-穿透（每目标只命中一次，最多穿透3个）</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2591,7 @@
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>1000500002:0.1</t>
+          <t>1000500002:0.25</t>
         </is>
       </c>
       <c r="H31" s="0" t="n">
@@ -2607,9 +2610,10 @@
       <c r="P31" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U31" s="0" t="n"/>
       <c r="W31" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%烧伤)</t>
+          <t>远程攻击-穿透火锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中25%烧伤)</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2634,7 @@
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>1000100002:0.1</t>
+          <t>1000100002:0.25</t>
         </is>
       </c>
       <c r="H32" s="0" t="n">
@@ -2649,9 +2653,10 @@
       <c r="P32" s="0" t="n">
         <v>420006</v>
       </c>
+      <c r="U32" s="0" t="n"/>
       <c r="W32" s="0" t="inlineStr">
         <is>
-          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中10%冰缓)</t>
+          <t>远程攻击-穿透冰锥-逐击衰减收缩(初始2倍,每穿1个伤害减半保底1/大小缩小1/3,降至1销毁;命中25%冰缓)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_info[攻击方式].xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
-          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给最前排3个友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
+          <t>援护护盾-瞬发施法(大盾战士BOSS技能:给1个最前排+其余随机友军套伤害转移护盾2000700001,经ext100005全局技能挂载,10秒一次)</t>
         </is>
       </c>
     </row>
